--- a/DASHBOARD COSTO LAVORO 2025-2026.xlsx
+++ b/DASHBOARD COSTO LAVORO 2025-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\dpiccoli\Kundalini Unipersonale\Collaboratori\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\dpiccoli\Kundalini Unipersonale\Collaboratori\DASH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{648C14DE-AF3C-42B9-8E24-4232B08A8A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE89FC2-05B5-4CC0-A586-0AE3E3C364D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="17400" xr2:uid="{0E1E5C30-1EA2-40EC-BCF7-60B4522243F2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="70">
   <si>
     <t>MESE</t>
   </si>
@@ -140,9 +140,6 @@
     <t>ORIANI MICOL</t>
   </si>
   <si>
-    <t>PICCOLI DANIELE GIOVANNI GIOACCHINO</t>
-  </si>
-  <si>
     <t>PONTINI MADDALENA</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>ISTRUTTORE/TRACCIATORE</t>
   </si>
   <si>
-    <t>CREPALDI MICHELE GIUSEPPE</t>
-  </si>
-  <si>
     <t>DE PRETO MARTINA</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
   </si>
   <si>
     <t>MOLIGNONI MARIO</t>
-  </si>
-  <si>
-    <t>MOLIGNONI MARIO LUIGI</t>
   </si>
   <si>
     <t>MORONI GABRIELE</t>
@@ -252,6 +243,12 @@
   </si>
   <si>
     <t>ARTARIA GIORGIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PICCOLI DANIELE </t>
+  </si>
+  <si>
+    <t>PICCOLI DANIELE</t>
   </si>
 </sst>
 </file>
@@ -642,7 +639,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
@@ -2836,7 +2833,7 @@
         <v>2025</v>
       </c>
       <c r="C110" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D110" t="s">
         <v>8</v>
@@ -2856,7 +2853,7 @@
         <v>2025</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D111" t="s">
         <v>8</v>
@@ -2876,7 +2873,7 @@
         <v>2025</v>
       </c>
       <c r="C112" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D112" t="s">
         <v>8</v>
@@ -2896,7 +2893,7 @@
         <v>2025</v>
       </c>
       <c r="C113" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D113" t="s">
         <v>8</v>
@@ -2916,7 +2913,7 @@
         <v>2025</v>
       </c>
       <c r="C114" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D114" t="s">
         <v>8</v>
@@ -2936,7 +2933,7 @@
         <v>2025</v>
       </c>
       <c r="C115" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D115" t="s">
         <v>8</v>
@@ -2956,7 +2953,7 @@
         <v>2025</v>
       </c>
       <c r="C116" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D116" t="s">
         <v>8</v>
@@ -2976,7 +2973,7 @@
         <v>2025</v>
       </c>
       <c r="C117" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D117" t="s">
         <v>8</v>
@@ -2996,7 +2993,7 @@
         <v>2025</v>
       </c>
       <c r="C118" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
@@ -3016,7 +3013,7 @@
         <v>2025</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -3036,7 +3033,7 @@
         <v>2025</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D120" t="s">
         <v>8</v>
@@ -3056,7 +3053,7 @@
         <v>2025</v>
       </c>
       <c r="C121" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D121" t="s">
         <v>8</v>
@@ -3076,7 +3073,7 @@
         <v>2025</v>
       </c>
       <c r="C122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D122" t="s">
         <v>8</v>
@@ -3096,7 +3093,7 @@
         <v>2025</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D123" t="s">
         <v>8</v>
@@ -3116,7 +3113,7 @@
         <v>2025</v>
       </c>
       <c r="C124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -3136,7 +3133,7 @@
         <v>2025</v>
       </c>
       <c r="C125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
@@ -3156,7 +3153,7 @@
         <v>2025</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
@@ -3176,10 +3173,10 @@
         <v>2025</v>
       </c>
       <c r="C127" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" t="s">
         <v>35</v>
-      </c>
-      <c r="D127" t="s">
-        <v>36</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -3196,10 +3193,10 @@
         <v>2025</v>
       </c>
       <c r="C128" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" t="s">
         <v>35</v>
-      </c>
-      <c r="D128" t="s">
-        <v>36</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -3216,10 +3213,10 @@
         <v>2025</v>
       </c>
       <c r="C129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" t="s">
         <v>35</v>
-      </c>
-      <c r="D129" t="s">
-        <v>36</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -3236,10 +3233,10 @@
         <v>2025</v>
       </c>
       <c r="C130" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130" t="s">
         <v>35</v>
-      </c>
-      <c r="D130" t="s">
-        <v>36</v>
       </c>
       <c r="E130" t="s">
         <v>25</v>
@@ -3256,10 +3253,10 @@
         <v>2025</v>
       </c>
       <c r="C131" t="s">
+        <v>34</v>
+      </c>
+      <c r="D131" t="s">
         <v>35</v>
-      </c>
-      <c r="D131" t="s">
-        <v>36</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -3276,10 +3273,10 @@
         <v>2025</v>
       </c>
       <c r="C132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D132" t="s">
         <v>35</v>
-      </c>
-      <c r="D132" t="s">
-        <v>36</v>
       </c>
       <c r="E132" t="s">
         <v>25</v>
@@ -3296,10 +3293,10 @@
         <v>2025</v>
       </c>
       <c r="C133" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" t="s">
         <v>35</v>
-      </c>
-      <c r="D133" t="s">
-        <v>36</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -3316,10 +3313,10 @@
         <v>2025</v>
       </c>
       <c r="C134" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" t="s">
         <v>35</v>
-      </c>
-      <c r="D134" t="s">
-        <v>36</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -3336,10 +3333,10 @@
         <v>2025</v>
       </c>
       <c r="C135" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" t="s">
         <v>35</v>
-      </c>
-      <c r="D135" t="s">
-        <v>36</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -3356,10 +3353,10 @@
         <v>2025</v>
       </c>
       <c r="C136" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" t="s">
         <v>35</v>
-      </c>
-      <c r="D136" t="s">
-        <v>36</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -3376,10 +3373,10 @@
         <v>2025</v>
       </c>
       <c r="C137" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" t="s">
         <v>35</v>
-      </c>
-      <c r="D137" t="s">
-        <v>36</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
@@ -3396,10 +3393,10 @@
         <v>2025</v>
       </c>
       <c r="C138" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" t="s">
         <v>35</v>
-      </c>
-      <c r="D138" t="s">
-        <v>36</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -3416,10 +3413,10 @@
         <v>2025</v>
       </c>
       <c r="C139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E139" t="s">
         <v>25</v>
@@ -3436,10 +3433,10 @@
         <v>2025</v>
       </c>
       <c r="C140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E140" t="s">
         <v>25</v>
@@ -3456,10 +3453,10 @@
         <v>2025</v>
       </c>
       <c r="C141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E141" t="s">
         <v>25</v>
@@ -3476,10 +3473,10 @@
         <v>2025</v>
       </c>
       <c r="C142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E142" t="s">
         <v>25</v>
@@ -3496,10 +3493,10 @@
         <v>2025</v>
       </c>
       <c r="C143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -3516,10 +3513,10 @@
         <v>2025</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -3536,10 +3533,10 @@
         <v>2025</v>
       </c>
       <c r="C145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -3556,10 +3553,10 @@
         <v>2025</v>
       </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
@@ -3576,10 +3573,10 @@
         <v>2025</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E147" t="s">
         <v>25</v>
@@ -3596,10 +3593,10 @@
         <v>2025</v>
       </c>
       <c r="C148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E148" t="s">
         <v>25</v>
@@ -3616,10 +3613,10 @@
         <v>2025</v>
       </c>
       <c r="C149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E149" t="s">
         <v>25</v>
@@ -3636,10 +3633,10 @@
         <v>2025</v>
       </c>
       <c r="C150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E150" t="s">
         <v>25</v>
@@ -3656,10 +3653,10 @@
         <v>2025</v>
       </c>
       <c r="C151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -3676,10 +3673,10 @@
         <v>2025</v>
       </c>
       <c r="C152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -3696,10 +3693,10 @@
         <v>2025</v>
       </c>
       <c r="C153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -3716,10 +3713,10 @@
         <v>2025</v>
       </c>
       <c r="C154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -3736,10 +3733,10 @@
         <v>2025</v>
       </c>
       <c r="C155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -3756,10 +3753,10 @@
         <v>2025</v>
       </c>
       <c r="C156" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -3776,10 +3773,10 @@
         <v>2025</v>
       </c>
       <c r="C157" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -3796,10 +3793,10 @@
         <v>2025</v>
       </c>
       <c r="C158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
@@ -3816,10 +3813,10 @@
         <v>2025</v>
       </c>
       <c r="C159" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D159" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E159" t="s">
         <v>9</v>
@@ -3836,10 +3833,10 @@
         <v>2025</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E160" t="s">
         <v>9</v>
@@ -3856,10 +3853,10 @@
         <v>2025</v>
       </c>
       <c r="C161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
@@ -3876,10 +3873,10 @@
         <v>2025</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
@@ -3896,13 +3893,13 @@
         <v>2025</v>
       </c>
       <c r="C163" t="s">
+        <v>38</v>
+      </c>
+      <c r="D163" t="s">
         <v>39</v>
       </c>
-      <c r="D163" t="s">
-        <v>40</v>
-      </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F163">
         <v>1456</v>
@@ -3916,13 +3913,13 @@
         <v>2025</v>
       </c>
       <c r="C164" t="s">
+        <v>38</v>
+      </c>
+      <c r="D164" t="s">
         <v>39</v>
       </c>
-      <c r="D164" t="s">
-        <v>40</v>
-      </c>
       <c r="E164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F164">
         <v>1560</v>
@@ -3936,13 +3933,13 @@
         <v>2025</v>
       </c>
       <c r="C165" t="s">
+        <v>38</v>
+      </c>
+      <c r="D165" t="s">
         <v>39</v>
       </c>
-      <c r="D165" t="s">
-        <v>40</v>
-      </c>
       <c r="E165" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F165">
         <v>1560</v>
@@ -3956,13 +3953,13 @@
         <v>2025</v>
       </c>
       <c r="C166" t="s">
+        <v>38</v>
+      </c>
+      <c r="D166" t="s">
         <v>39</v>
       </c>
-      <c r="D166" t="s">
-        <v>40</v>
-      </c>
       <c r="E166" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F166">
         <v>1560</v>
@@ -3976,13 +3973,13 @@
         <v>2025</v>
       </c>
       <c r="C167" t="s">
+        <v>38</v>
+      </c>
+      <c r="D167" t="s">
         <v>39</v>
       </c>
-      <c r="D167" t="s">
-        <v>40</v>
-      </c>
       <c r="E167" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F167">
         <v>1560</v>
@@ -3996,13 +3993,13 @@
         <v>2025</v>
       </c>
       <c r="C168" t="s">
+        <v>38</v>
+      </c>
+      <c r="D168" t="s">
         <v>39</v>
       </c>
-      <c r="D168" t="s">
-        <v>40</v>
-      </c>
       <c r="E168" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F168">
         <v>1560</v>
@@ -4016,13 +4013,13 @@
         <v>2025</v>
       </c>
       <c r="C169" t="s">
+        <v>38</v>
+      </c>
+      <c r="D169" t="s">
         <v>39</v>
       </c>
-      <c r="D169" t="s">
-        <v>40</v>
-      </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F169">
         <v>1820</v>
@@ -4036,13 +4033,13 @@
         <v>2025</v>
       </c>
       <c r="C170" t="s">
+        <v>38</v>
+      </c>
+      <c r="D170" t="s">
         <v>39</v>
       </c>
-      <c r="D170" t="s">
-        <v>40</v>
-      </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F170">
         <v>1820</v>
@@ -4056,13 +4053,13 @@
         <v>2025</v>
       </c>
       <c r="C171" t="s">
+        <v>38</v>
+      </c>
+      <c r="D171" t="s">
         <v>39</v>
       </c>
-      <c r="D171" t="s">
-        <v>40</v>
-      </c>
       <c r="E171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F171">
         <v>1820</v>
@@ -4076,13 +4073,13 @@
         <v>2025</v>
       </c>
       <c r="C172" t="s">
+        <v>38</v>
+      </c>
+      <c r="D172" t="s">
         <v>39</v>
       </c>
-      <c r="D172" t="s">
-        <v>40</v>
-      </c>
       <c r="E172" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F172">
         <v>1820</v>
@@ -4096,13 +4093,13 @@
         <v>2025</v>
       </c>
       <c r="C173" t="s">
+        <v>38</v>
+      </c>
+      <c r="D173" t="s">
         <v>39</v>
       </c>
-      <c r="D173" t="s">
-        <v>40</v>
-      </c>
       <c r="E173" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F173">
         <v>1820</v>
@@ -4116,13 +4113,13 @@
         <v>2025</v>
       </c>
       <c r="C174" t="s">
+        <v>38</v>
+      </c>
+      <c r="D174" t="s">
         <v>39</v>
       </c>
-      <c r="D174" t="s">
-        <v>40</v>
-      </c>
       <c r="E174" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F174">
         <v>1820</v>
@@ -4136,13 +4133,13 @@
         <v>2025</v>
       </c>
       <c r="C175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D175" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F175">
         <v>3333</v>
@@ -4156,13 +4153,13 @@
         <v>2025</v>
       </c>
       <c r="C176" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D176" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E176" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F176">
         <v>3333</v>
@@ -4176,13 +4173,13 @@
         <v>2025</v>
       </c>
       <c r="C177" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D177" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E177" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F177">
         <v>3333</v>
@@ -4196,13 +4193,13 @@
         <v>2025</v>
       </c>
       <c r="C178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E178" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F178">
         <v>3333</v>
@@ -4216,13 +4213,13 @@
         <v>2025</v>
       </c>
       <c r="C179" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D179" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E179" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F179">
         <v>3333</v>
@@ -4236,13 +4233,13 @@
         <v>2025</v>
       </c>
       <c r="C180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D180" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E180" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F180">
         <v>3333</v>
@@ -4256,13 +4253,13 @@
         <v>2025</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D181" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E181" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F181">
         <v>3333</v>
@@ -4276,13 +4273,13 @@
         <v>2025</v>
       </c>
       <c r="C182" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F182">
         <v>3333</v>
@@ -4296,13 +4293,13 @@
         <v>2025</v>
       </c>
       <c r="C183" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F183">
         <v>3333</v>
@@ -4316,13 +4313,13 @@
         <v>2025</v>
       </c>
       <c r="C184" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D184" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E184" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F184">
         <v>3333</v>
@@ -4336,13 +4333,13 @@
         <v>2025</v>
       </c>
       <c r="C185" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E185" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F185">
         <v>3469</v>
@@ -4356,13 +4353,13 @@
         <v>2025</v>
       </c>
       <c r="C186" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D186" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E186" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F186">
         <v>3833</v>
@@ -4376,13 +4373,13 @@
         <v>2025</v>
       </c>
       <c r="C187" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D187" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E187" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F187">
         <v>68</v>
@@ -4396,13 +4393,13 @@
         <v>2025</v>
       </c>
       <c r="C188" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D188" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F188">
         <v>154</v>
@@ -4416,13 +4413,13 @@
         <v>2025</v>
       </c>
       <c r="C189" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D189" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E189" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F189">
         <v>157</v>
@@ -4436,13 +4433,13 @@
         <v>2025</v>
       </c>
       <c r="C190" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D190" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E190" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F190">
         <v>180</v>
@@ -4456,13 +4453,13 @@
         <v>2025</v>
       </c>
       <c r="C191" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D191" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E191" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F191">
         <v>181</v>
@@ -4476,13 +4473,13 @@
         <v>2025</v>
       </c>
       <c r="C192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D192" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E192" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F192">
         <v>230</v>
@@ -4496,13 +4493,13 @@
         <v>2025</v>
       </c>
       <c r="C193" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D193" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E193" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F193">
         <v>286</v>
@@ -4516,13 +4513,13 @@
         <v>2025</v>
       </c>
       <c r="C194" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D194" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E194" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F194">
         <v>318</v>
@@ -4536,13 +4533,13 @@
         <v>2025</v>
       </c>
       <c r="C195" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D195" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E195" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F195">
         <v>436</v>
@@ -4556,13 +4553,13 @@
         <v>2025</v>
       </c>
       <c r="C196" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D196" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F196">
         <v>485</v>
@@ -4576,13 +4573,13 @@
         <v>2025</v>
       </c>
       <c r="C197" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D197" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F197">
         <v>150</v>
@@ -4596,13 +4593,13 @@
         <v>2025</v>
       </c>
       <c r="C198" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D198" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E198" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F198">
         <v>205</v>
@@ -4616,13 +4613,13 @@
         <v>2025</v>
       </c>
       <c r="C199" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D199" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E199" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F199">
         <v>216</v>
@@ -4636,13 +4633,13 @@
         <v>2025</v>
       </c>
       <c r="C200" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D200" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E200" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F200">
         <v>274</v>
@@ -4656,13 +4653,13 @@
         <v>2025</v>
       </c>
       <c r="C201" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D201" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E201" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F201">
         <v>317</v>
@@ -4676,13 +4673,13 @@
         <v>2025</v>
       </c>
       <c r="C202" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D202" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E202" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F202">
         <v>331</v>
@@ -4696,13 +4693,13 @@
         <v>2025</v>
       </c>
       <c r="C203" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D203" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E203" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F203">
         <v>496</v>
@@ -4716,13 +4713,13 @@
         <v>2025</v>
       </c>
       <c r="C204" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D204" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E204" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F204">
         <v>543</v>
@@ -4736,13 +4733,13 @@
         <v>2025</v>
       </c>
       <c r="C205" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D205" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E205" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F205">
         <v>604</v>
@@ -4756,13 +4753,13 @@
         <v>2025</v>
       </c>
       <c r="C206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D206" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E206" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F206">
         <v>706</v>
@@ -4776,13 +4773,13 @@
         <v>2025</v>
       </c>
       <c r="C207" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E207" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F207">
         <v>40</v>
@@ -4796,13 +4793,13 @@
         <v>2025</v>
       </c>
       <c r="C208" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D208" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E208" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F208">
         <v>88</v>
@@ -4816,13 +4813,13 @@
         <v>2025</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D209" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E209" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F209">
         <v>45</v>
@@ -4836,13 +4833,13 @@
         <v>2025</v>
       </c>
       <c r="C210" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D210" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E210" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F210">
         <v>45</v>
@@ -4856,13 +4853,13 @@
         <v>2025</v>
       </c>
       <c r="C211" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D211" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E211" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F211">
         <v>135</v>
@@ -4876,13 +4873,13 @@
         <v>2025</v>
       </c>
       <c r="C212" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D212" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E212" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F212">
         <v>188</v>
@@ -4896,13 +4893,13 @@
         <v>2025</v>
       </c>
       <c r="C213" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D213" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E213" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F213">
         <v>378</v>
@@ -4916,13 +4913,13 @@
         <v>2025</v>
       </c>
       <c r="C214" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D214" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E214" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F214">
         <v>471</v>
@@ -4936,13 +4933,13 @@
         <v>2025</v>
       </c>
       <c r="C215" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D215" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E215" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F215">
         <v>591</v>
@@ -4956,13 +4953,13 @@
         <v>2025</v>
       </c>
       <c r="C216" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D216" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E216" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F216">
         <v>608</v>
@@ -4976,13 +4973,13 @@
         <v>2025</v>
       </c>
       <c r="C217" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D217" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E217" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F217">
         <v>712</v>
@@ -4996,13 +4993,13 @@
         <v>2025</v>
       </c>
       <c r="C218" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D218" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E218" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F218">
         <v>778</v>
@@ -5016,13 +5013,13 @@
         <v>2025</v>
       </c>
       <c r="C219" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D219" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E219" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F219">
         <v>469</v>
@@ -5036,13 +5033,13 @@
         <v>2025</v>
       </c>
       <c r="C220" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D220" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E220" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F220">
         <v>1001</v>
@@ -5056,13 +5053,13 @@
         <v>2025</v>
       </c>
       <c r="C221" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D221" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E221" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F221">
         <v>1396</v>
@@ -5076,13 +5073,13 @@
         <v>2025</v>
       </c>
       <c r="C222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D222" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E222" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F222">
         <v>1667</v>
@@ -5096,13 +5093,13 @@
         <v>2025</v>
       </c>
       <c r="C223" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D223" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E223" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F223">
         <v>1679</v>
@@ -5116,13 +5113,13 @@
         <v>2025</v>
       </c>
       <c r="C224" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D224" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E224" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F224">
         <v>1744</v>
@@ -5136,13 +5133,13 @@
         <v>2025</v>
       </c>
       <c r="C225" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D225" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E225" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F225">
         <v>1822</v>
@@ -5156,13 +5153,13 @@
         <v>2025</v>
       </c>
       <c r="C226" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D226" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E226" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F226">
         <v>1910</v>
@@ -5176,13 +5173,13 @@
         <v>2025</v>
       </c>
       <c r="C227" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D227" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E227" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F227">
         <v>2011</v>
@@ -5196,13 +5193,13 @@
         <v>2025</v>
       </c>
       <c r="C228" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D228" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E228" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F228">
         <v>2286</v>
@@ -5216,13 +5213,13 @@
         <v>2025</v>
       </c>
       <c r="C229" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D229" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E229" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F229">
         <v>2510</v>
@@ -5236,13 +5233,13 @@
         <v>2025</v>
       </c>
       <c r="C230" t="s">
+        <v>48</v>
+      </c>
+      <c r="D230" t="s">
+        <v>43</v>
+      </c>
+      <c r="E230" t="s">
         <v>49</v>
-      </c>
-      <c r="D230" t="s">
-        <v>44</v>
-      </c>
-      <c r="E230" t="s">
-        <v>50</v>
       </c>
       <c r="F230">
         <v>424</v>
@@ -5256,13 +5253,13 @@
         <v>2025</v>
       </c>
       <c r="C231" t="s">
+        <v>48</v>
+      </c>
+      <c r="D231" t="s">
+        <v>43</v>
+      </c>
+      <c r="E231" t="s">
         <v>49</v>
-      </c>
-      <c r="D231" t="s">
-        <v>44</v>
-      </c>
-      <c r="E231" t="s">
-        <v>50</v>
       </c>
       <c r="F231">
         <v>1343</v>
@@ -5276,13 +5273,13 @@
         <v>2025</v>
       </c>
       <c r="C232" t="s">
+        <v>48</v>
+      </c>
+      <c r="D232" t="s">
+        <v>43</v>
+      </c>
+      <c r="E232" t="s">
         <v>49</v>
-      </c>
-      <c r="D232" t="s">
-        <v>44</v>
-      </c>
-      <c r="E232" t="s">
-        <v>50</v>
       </c>
       <c r="F232">
         <v>1365</v>
@@ -5296,13 +5293,13 @@
         <v>2025</v>
       </c>
       <c r="C233" t="s">
+        <v>48</v>
+      </c>
+      <c r="D233" t="s">
+        <v>43</v>
+      </c>
+      <c r="E233" t="s">
         <v>49</v>
-      </c>
-      <c r="D233" t="s">
-        <v>44</v>
-      </c>
-      <c r="E233" t="s">
-        <v>50</v>
       </c>
       <c r="F233">
         <v>1391</v>
@@ -5316,13 +5313,13 @@
         <v>2025</v>
       </c>
       <c r="C234" t="s">
+        <v>48</v>
+      </c>
+      <c r="D234" t="s">
+        <v>43</v>
+      </c>
+      <c r="E234" t="s">
         <v>49</v>
-      </c>
-      <c r="D234" t="s">
-        <v>44</v>
-      </c>
-      <c r="E234" t="s">
-        <v>50</v>
       </c>
       <c r="F234">
         <v>1416</v>
@@ -5336,13 +5333,13 @@
         <v>2025</v>
       </c>
       <c r="C235" t="s">
+        <v>48</v>
+      </c>
+      <c r="D235" t="s">
+        <v>43</v>
+      </c>
+      <c r="E235" t="s">
         <v>49</v>
-      </c>
-      <c r="D235" t="s">
-        <v>44</v>
-      </c>
-      <c r="E235" t="s">
-        <v>50</v>
       </c>
       <c r="F235">
         <v>1509</v>
@@ -5356,13 +5353,13 @@
         <v>2025</v>
       </c>
       <c r="C236" t="s">
+        <v>48</v>
+      </c>
+      <c r="D236" t="s">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
         <v>49</v>
-      </c>
-      <c r="D236" t="s">
-        <v>44</v>
-      </c>
-      <c r="E236" t="s">
-        <v>50</v>
       </c>
       <c r="F236">
         <v>1588</v>
@@ -5376,13 +5373,13 @@
         <v>2025</v>
       </c>
       <c r="C237" t="s">
+        <v>48</v>
+      </c>
+      <c r="D237" t="s">
+        <v>43</v>
+      </c>
+      <c r="E237" t="s">
         <v>49</v>
-      </c>
-      <c r="D237" t="s">
-        <v>44</v>
-      </c>
-      <c r="E237" t="s">
-        <v>50</v>
       </c>
       <c r="F237">
         <v>1828</v>
@@ -5396,13 +5393,13 @@
         <v>2025</v>
       </c>
       <c r="C238" t="s">
+        <v>48</v>
+      </c>
+      <c r="D238" t="s">
+        <v>43</v>
+      </c>
+      <c r="E238" t="s">
         <v>49</v>
-      </c>
-      <c r="D238" t="s">
-        <v>44</v>
-      </c>
-      <c r="E238" t="s">
-        <v>50</v>
       </c>
       <c r="F238">
         <v>1932</v>
@@ -5416,13 +5413,13 @@
         <v>2025</v>
       </c>
       <c r="C239" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D239" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E239" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F239">
         <v>1785</v>
@@ -5436,13 +5433,13 @@
         <v>2025</v>
       </c>
       <c r="C240" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D240" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E240" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F240">
         <v>1872</v>
@@ -5456,13 +5453,13 @@
         <v>2025</v>
       </c>
       <c r="C241" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D241" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E241" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F241">
         <v>2942</v>
@@ -5476,13 +5473,13 @@
         <v>2025</v>
       </c>
       <c r="C242" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E242" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F242">
         <v>103</v>
@@ -5496,13 +5493,13 @@
         <v>2025</v>
       </c>
       <c r="C243" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D243" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E243" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F243">
         <v>292</v>
@@ -5516,13 +5513,13 @@
         <v>2025</v>
       </c>
       <c r="C244" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E244" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F244">
         <v>617</v>
@@ -5536,13 +5533,13 @@
         <v>2025</v>
       </c>
       <c r="C245" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D245" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E245" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F245">
         <v>691</v>
@@ -5556,13 +5553,13 @@
         <v>2025</v>
       </c>
       <c r="C246" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D246" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E246" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F246">
         <v>1009</v>
@@ -5576,13 +5573,13 @@
         <v>2025</v>
       </c>
       <c r="C247" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E247" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F247">
         <v>1056</v>
@@ -5596,13 +5593,13 @@
         <v>2025</v>
       </c>
       <c r="C248" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D248" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E248" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F248">
         <v>349</v>
@@ -5616,13 +5613,13 @@
         <v>2025</v>
       </c>
       <c r="C249" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D249" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E249" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F249">
         <v>799</v>
@@ -5636,13 +5633,13 @@
         <v>2025</v>
       </c>
       <c r="C250" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D250" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E250" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F250">
         <v>1215</v>
@@ -5656,13 +5653,13 @@
         <v>2025</v>
       </c>
       <c r="C251" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D251" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E251" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F251">
         <v>1232</v>
@@ -5676,13 +5673,13 @@
         <v>2025</v>
       </c>
       <c r="C252" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D252" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E252" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F252">
         <v>1339</v>
@@ -5696,13 +5693,13 @@
         <v>2025</v>
       </c>
       <c r="C253" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D253" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E253" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F253">
         <v>1734</v>
@@ -5716,13 +5713,13 @@
         <v>2025</v>
       </c>
       <c r="C254" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D254" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E254" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F254">
         <v>1763</v>
@@ -5736,13 +5733,13 @@
         <v>2025</v>
       </c>
       <c r="C255" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D255" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E255" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F255">
         <v>1835</v>
@@ -5756,13 +5753,13 @@
         <v>2025</v>
       </c>
       <c r="C256" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D256" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E256" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F256">
         <v>1935</v>
@@ -5776,13 +5773,13 @@
         <v>2025</v>
       </c>
       <c r="C257" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D257" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E257" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F257">
         <v>2046</v>
@@ -5796,13 +5793,13 @@
         <v>2025</v>
       </c>
       <c r="C258" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D258" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E258" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F258">
         <v>2050</v>
@@ -5816,13 +5813,13 @@
         <v>2025</v>
       </c>
       <c r="C259" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D259" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E259" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F259">
         <v>2118</v>
@@ -5836,13 +5833,13 @@
         <v>2025</v>
       </c>
       <c r="C260" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D260" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E260" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F260">
         <v>162</v>
@@ -5856,13 +5853,13 @@
         <v>2025</v>
       </c>
       <c r="C261" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D261" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E261" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F261">
         <v>254</v>
@@ -5876,13 +5873,13 @@
         <v>2025</v>
       </c>
       <c r="C262" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D262" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E262" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F262">
         <v>378</v>
@@ -5896,13 +5893,13 @@
         <v>2025</v>
       </c>
       <c r="C263" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D263" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E263" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F263">
         <v>381</v>
@@ -5916,13 +5913,13 @@
         <v>2025</v>
       </c>
       <c r="C264" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D264" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E264" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F264">
         <v>396</v>
@@ -5936,13 +5933,13 @@
         <v>2025</v>
       </c>
       <c r="C265" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D265" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E265" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F265">
         <v>434</v>
@@ -5956,13 +5953,13 @@
         <v>2025</v>
       </c>
       <c r="C266" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D266" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E266" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F266">
         <v>546</v>
@@ -5976,13 +5973,13 @@
         <v>2025</v>
       </c>
       <c r="C267" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D267" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E267" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F267">
         <v>552</v>
@@ -5996,13 +5993,13 @@
         <v>2025</v>
       </c>
       <c r="C268" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D268" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E268" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F268">
         <v>636</v>
@@ -6016,13 +6013,13 @@
         <v>2025</v>
       </c>
       <c r="C269" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D269" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E269" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F269">
         <v>704</v>
@@ -6036,13 +6033,13 @@
         <v>2025</v>
       </c>
       <c r="C270" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D270" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E270" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F270">
         <v>768</v>
@@ -6056,13 +6053,13 @@
         <v>2025</v>
       </c>
       <c r="C271" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D271" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E271" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F271">
         <v>1100</v>
@@ -6076,13 +6073,13 @@
         <v>2025</v>
       </c>
       <c r="C272" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D272" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E272" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F272">
         <v>149</v>
@@ -6096,13 +6093,13 @@
         <v>2025</v>
       </c>
       <c r="C273" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D273" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E273" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F273">
         <v>234</v>
@@ -6116,13 +6113,13 @@
         <v>2025</v>
       </c>
       <c r="C274" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D274" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E274" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F274">
         <v>278</v>
@@ -6136,13 +6133,13 @@
         <v>2025</v>
       </c>
       <c r="C275" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D275" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E275" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F275">
         <v>400</v>
@@ -6156,13 +6153,13 @@
         <v>2025</v>
       </c>
       <c r="C276" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D276" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E276" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F276">
         <v>414</v>
@@ -6176,13 +6173,13 @@
         <v>2025</v>
       </c>
       <c r="C277" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D277" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E277" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F277">
         <v>489</v>
@@ -6196,13 +6193,13 @@
         <v>2025</v>
       </c>
       <c r="C278" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D278" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E278" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F278">
         <v>225</v>
@@ -6216,13 +6213,13 @@
         <v>2025</v>
       </c>
       <c r="C279" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D279" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E279" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F279">
         <v>280</v>
@@ -6236,13 +6233,13 @@
         <v>2025</v>
       </c>
       <c r="C280" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D280" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E280" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F280">
         <v>390</v>
@@ -6256,13 +6253,13 @@
         <v>2025</v>
       </c>
       <c r="C281" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D281" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E281" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F281">
         <v>460</v>
@@ -6276,13 +6273,13 @@
         <v>2025</v>
       </c>
       <c r="C282" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D282" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E282" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F282">
         <v>511</v>
@@ -6296,13 +6293,13 @@
         <v>2025</v>
       </c>
       <c r="C283" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D283" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E283" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F283">
         <v>541</v>
@@ -6316,13 +6313,13 @@
         <v>2025</v>
       </c>
       <c r="C284" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D284" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E284" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F284">
         <v>571</v>
@@ -6336,13 +6333,13 @@
         <v>2025</v>
       </c>
       <c r="C285" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D285" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E285" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F285">
         <v>615</v>
@@ -6356,13 +6353,13 @@
         <v>2025</v>
       </c>
       <c r="C286" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D286" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E286" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F286">
         <v>619</v>
@@ -6376,13 +6373,13 @@
         <v>2025</v>
       </c>
       <c r="C287" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E287" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F287">
         <v>681</v>
@@ -6399,10 +6396,10 @@
         <v>30</v>
       </c>
       <c r="D288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E288" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F288">
         <v>146</v>
@@ -6419,10 +6416,10 @@
         <v>30</v>
       </c>
       <c r="D289" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E289" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F289">
         <v>195</v>
@@ -6439,10 +6436,10 @@
         <v>30</v>
       </c>
       <c r="D290" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E290" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F290">
         <v>362</v>
@@ -6459,10 +6456,10 @@
         <v>30</v>
       </c>
       <c r="D291" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E291" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F291">
         <v>591</v>
@@ -6479,10 +6476,10 @@
         <v>30</v>
       </c>
       <c r="D292" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E292" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F292">
         <v>730</v>
@@ -6499,10 +6496,10 @@
         <v>30</v>
       </c>
       <c r="D293" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E293" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F293">
         <v>833</v>
@@ -6519,10 +6516,10 @@
         <v>30</v>
       </c>
       <c r="D294" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E294" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F294">
         <v>944</v>
@@ -6539,10 +6536,10 @@
         <v>30</v>
       </c>
       <c r="D295" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E295" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F295">
         <v>1746</v>
@@ -6556,13 +6553,13 @@
         <v>2025</v>
       </c>
       <c r="C296" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D296" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E296" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F296">
         <v>116</v>
@@ -6576,13 +6573,13 @@
         <v>2025</v>
       </c>
       <c r="C297" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D297" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E297" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F297">
         <v>576</v>
@@ -6596,13 +6593,13 @@
         <v>2025</v>
       </c>
       <c r="C298" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D298" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E298" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F298">
         <v>1699</v>
@@ -6616,13 +6613,13 @@
         <v>2025</v>
       </c>
       <c r="C299" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D299" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E299" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F299">
         <v>2063</v>
@@ -6636,13 +6633,13 @@
         <v>2025</v>
       </c>
       <c r="C300" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D300" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E300" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F300">
         <v>2065</v>
@@ -6656,13 +6653,13 @@
         <v>2025</v>
       </c>
       <c r="C301" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D301" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E301" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F301">
         <v>2288</v>
@@ -6676,13 +6673,13 @@
         <v>2025</v>
       </c>
       <c r="C302" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D302" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E302" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F302">
         <v>2419</v>
@@ -6696,13 +6693,13 @@
         <v>2025</v>
       </c>
       <c r="C303" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D303" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E303" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F303">
         <v>4388</v>
@@ -6716,13 +6713,13 @@
         <v>2025</v>
       </c>
       <c r="C304" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D304" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E304" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F304">
         <v>1650</v>
@@ -6736,13 +6733,13 @@
         <v>2025</v>
       </c>
       <c r="C305" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D305" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E305" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F305">
         <v>2002</v>
@@ -6756,13 +6753,13 @@
         <v>2025</v>
       </c>
       <c r="C306" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D306" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E306" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F306">
         <v>2002</v>
@@ -6776,13 +6773,13 @@
         <v>2025</v>
       </c>
       <c r="C307" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D307" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E307" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F307">
         <v>1500</v>
@@ -6796,13 +6793,13 @@
         <v>2025</v>
       </c>
       <c r="C308" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D308" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E308" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F308">
         <v>1500</v>
@@ -6816,13 +6813,13 @@
         <v>2025</v>
       </c>
       <c r="C309" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D309" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E309" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F309">
         <v>1500</v>
@@ -6836,13 +6833,13 @@
         <v>2025</v>
       </c>
       <c r="C310" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D310" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E310" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F310">
         <v>1597</v>
@@ -6856,13 +6853,13 @@
         <v>2025</v>
       </c>
       <c r="C311" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D311" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E311" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F311">
         <v>1645</v>
@@ -6876,13 +6873,13 @@
         <v>2025</v>
       </c>
       <c r="C312" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D312" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E312" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F312">
         <v>1645</v>
@@ -6896,13 +6893,13 @@
         <v>2025</v>
       </c>
       <c r="C313" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D313" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E313" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F313">
         <v>1645</v>
@@ -6916,13 +6913,13 @@
         <v>2025</v>
       </c>
       <c r="C314" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D314" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E314" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F314">
         <v>1645</v>
@@ -6936,13 +6933,13 @@
         <v>2025</v>
       </c>
       <c r="C315" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D315" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E315" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F315">
         <v>1645</v>
@@ -6956,13 +6953,13 @@
         <v>2025</v>
       </c>
       <c r="C316" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D316" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E316" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F316">
         <v>2194</v>
@@ -6976,13 +6973,13 @@
         <v>2025</v>
       </c>
       <c r="C317" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D317" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E317" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F317">
         <v>2194</v>
@@ -6996,13 +6993,13 @@
         <v>2025</v>
       </c>
       <c r="C318" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D318" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E318" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F318">
         <v>3291</v>
@@ -7016,13 +7013,13 @@
         <v>2025</v>
       </c>
       <c r="C319" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D319" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E319" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F319">
         <v>69</v>
@@ -7036,13 +7033,13 @@
         <v>2025</v>
       </c>
       <c r="C320" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D320" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E320" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F320">
         <v>143</v>
@@ -7056,13 +7053,13 @@
         <v>2025</v>
       </c>
       <c r="C321" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D321" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E321" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F321">
         <v>160</v>
@@ -7076,13 +7073,13 @@
         <v>2025</v>
       </c>
       <c r="C322" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D322" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E322" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F322">
         <v>180</v>
@@ -7096,13 +7093,13 @@
         <v>2025</v>
       </c>
       <c r="C323" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D323" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E323" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F323">
         <v>256</v>
@@ -7116,13 +7113,13 @@
         <v>2025</v>
       </c>
       <c r="C324" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D324" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E324" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F324">
         <v>270</v>
@@ -7136,13 +7133,13 @@
         <v>2025</v>
       </c>
       <c r="C325" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D325" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E325" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F325">
         <v>366</v>
@@ -7156,13 +7153,13 @@
         <v>2025</v>
       </c>
       <c r="C326" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D326" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E326" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F326">
         <v>369</v>
@@ -7176,13 +7173,13 @@
         <v>2025</v>
       </c>
       <c r="C327" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D327" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E327" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F327">
         <v>387</v>
@@ -7196,13 +7193,13 @@
         <v>2025</v>
       </c>
       <c r="C328" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D328" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E328" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F328">
         <v>455</v>
@@ -7216,13 +7213,13 @@
         <v>2025</v>
       </c>
       <c r="C329" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D329" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E329" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F329">
         <v>240</v>
@@ -7236,13 +7233,13 @@
         <v>2025</v>
       </c>
       <c r="C330" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D330" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E330" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F330">
         <v>324</v>
@@ -7256,13 +7253,13 @@
         <v>2025</v>
       </c>
       <c r="C331" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D331" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E331" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F331">
         <v>389</v>
@@ -7276,13 +7273,13 @@
         <v>2025</v>
       </c>
       <c r="C332" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D332" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E332" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F332">
         <v>662</v>
@@ -7296,13 +7293,13 @@
         <v>2025</v>
       </c>
       <c r="C333" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D333" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E333" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F333">
         <v>168</v>
@@ -7316,13 +7313,13 @@
         <v>2025</v>
       </c>
       <c r="C334" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D334" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E334" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F334">
         <v>646</v>
@@ -7336,13 +7333,13 @@
         <v>2025</v>
       </c>
       <c r="C335" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D335" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E335" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F335">
         <v>999</v>
@@ -7356,13 +7353,13 @@
         <v>2025</v>
       </c>
       <c r="C336" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D336" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E336" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F336">
         <v>1192</v>
@@ -7376,13 +7373,13 @@
         <v>2025</v>
       </c>
       <c r="C337" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D337" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E337" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F337">
         <v>1333</v>
@@ -7396,13 +7393,13 @@
         <v>2025</v>
       </c>
       <c r="C338" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D338" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E338" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F338">
         <v>1344</v>
@@ -7416,13 +7413,13 @@
         <v>2025</v>
       </c>
       <c r="C339" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D339" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E339" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F339">
         <v>1445</v>
@@ -7436,13 +7433,13 @@
         <v>2025</v>
       </c>
       <c r="C340" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D340" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E340" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F340">
         <v>1544</v>
@@ -7456,13 +7453,13 @@
         <v>2025</v>
       </c>
       <c r="C341" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D341" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E341" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F341">
         <v>1687</v>
@@ -7476,13 +7473,13 @@
         <v>2025</v>
       </c>
       <c r="C342" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D342" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E342" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F342">
         <v>1838</v>
@@ -7496,13 +7493,13 @@
         <v>2025</v>
       </c>
       <c r="C343" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D343" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E343" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F343">
         <v>2002</v>
@@ -7516,13 +7513,13 @@
         <v>2025</v>
       </c>
       <c r="C344" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D344" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E344" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F344">
         <v>2039</v>
@@ -7536,13 +7533,13 @@
         <v>2025</v>
       </c>
       <c r="C345" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D345" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E345" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F345">
         <v>378</v>
@@ -7556,13 +7553,13 @@
         <v>2025</v>
       </c>
       <c r="C346" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D346" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E346" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F346">
         <v>394</v>
@@ -7576,13 +7573,13 @@
         <v>2025</v>
       </c>
       <c r="C347" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D347" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E347" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F347">
         <v>435</v>
@@ -7596,13 +7593,13 @@
         <v>2025</v>
       </c>
       <c r="C348" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D348" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E348" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F348">
         <v>643</v>
@@ -7616,13 +7613,13 @@
         <v>2025</v>
       </c>
       <c r="C349" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D349" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E349" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F349">
         <v>646</v>
@@ -7636,13 +7633,13 @@
         <v>2025</v>
       </c>
       <c r="C350" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D350" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E350" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F350">
         <v>699</v>
@@ -7656,13 +7653,13 @@
         <v>2025</v>
       </c>
       <c r="C351" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D351" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E351" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F351">
         <v>815</v>
@@ -7676,13 +7673,13 @@
         <v>2025</v>
       </c>
       <c r="C352" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D352" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E352" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F352">
         <v>997</v>
@@ -7696,13 +7693,13 @@
         <v>2025</v>
       </c>
       <c r="C353" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D353" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E353" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F353">
         <v>1010</v>
@@ -7716,13 +7713,13 @@
         <v>2025</v>
       </c>
       <c r="C354" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D354" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E354" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F354">
         <v>1063</v>
@@ -7736,13 +7733,13 @@
         <v>2025</v>
       </c>
       <c r="C355" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D355" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E355" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F355">
         <v>1077</v>
@@ -7756,13 +7753,13 @@
         <v>2025</v>
       </c>
       <c r="C356" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D356" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E356" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F356">
         <v>1114</v>
@@ -7776,13 +7773,13 @@
         <v>2025</v>
       </c>
       <c r="C357" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D357" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F357">
         <v>129</v>
@@ -7796,13 +7793,13 @@
         <v>2025</v>
       </c>
       <c r="C358" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D358" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F358">
         <v>233</v>
@@ -7816,13 +7813,13 @@
         <v>2025</v>
       </c>
       <c r="C359" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D359" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E359" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F359">
         <v>622</v>
@@ -7836,13 +7833,13 @@
         <v>2025</v>
       </c>
       <c r="C360" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D360" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E360" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F360">
         <v>679</v>
@@ -7856,13 +7853,13 @@
         <v>2025</v>
       </c>
       <c r="C361" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D361" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E361" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F361">
         <v>1521</v>
@@ -7876,13 +7873,13 @@
         <v>2025</v>
       </c>
       <c r="C362" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D362" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E362" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F362">
         <v>122</v>
@@ -7896,13 +7893,13 @@
         <v>2025</v>
       </c>
       <c r="C363" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D363" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F363">
         <v>180</v>
@@ -7916,13 +7913,13 @@
         <v>2025</v>
       </c>
       <c r="C364" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D364" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E364" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F364">
         <v>180</v>
@@ -7936,13 +7933,13 @@
         <v>2025</v>
       </c>
       <c r="C365" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D365" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E365" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F365">
         <v>226</v>
@@ -7956,13 +7953,13 @@
         <v>2025</v>
       </c>
       <c r="C366" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D366" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E366" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F366">
         <v>300</v>
@@ -7976,13 +7973,13 @@
         <v>2025</v>
       </c>
       <c r="C367" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D367" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E367" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F367">
         <v>316</v>
@@ -7996,13 +7993,13 @@
         <v>2025</v>
       </c>
       <c r="C368" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D368" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E368" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F368">
         <v>354</v>
@@ -8016,13 +8013,13 @@
         <v>2025</v>
       </c>
       <c r="C369" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D369" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E369" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F369">
         <v>380</v>
@@ -8036,13 +8033,13 @@
         <v>2025</v>
       </c>
       <c r="C370" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D370" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E370" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F370">
         <v>126</v>
@@ -8056,13 +8053,13 @@
         <v>2025</v>
       </c>
       <c r="C371" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D371" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E371" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F371">
         <v>161</v>
@@ -8076,13 +8073,13 @@
         <v>2025</v>
       </c>
       <c r="C372" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D372" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E372" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F372">
         <v>171</v>
@@ -8096,13 +8093,13 @@
         <v>2025</v>
       </c>
       <c r="C373" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D373" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E373" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F373">
         <v>183</v>
@@ -8116,13 +8113,13 @@
         <v>2025</v>
       </c>
       <c r="C374" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D374" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E374" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F374">
         <v>271</v>
@@ -8136,13 +8133,13 @@
         <v>2025</v>
       </c>
       <c r="C375" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D375" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E375" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F375">
         <v>301</v>
@@ -8156,13 +8153,13 @@
         <v>2025</v>
       </c>
       <c r="C376" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D376" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E376" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F376">
         <v>312</v>
@@ -8176,13 +8173,13 @@
         <v>2025</v>
       </c>
       <c r="C377" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D377" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E377" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F377">
         <v>323</v>
@@ -8196,13 +8193,13 @@
         <v>2025</v>
       </c>
       <c r="C378" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D378" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E378" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F378">
         <v>331</v>
@@ -8216,13 +8213,13 @@
         <v>2025</v>
       </c>
       <c r="C379" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D379" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E379" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F379">
         <v>519</v>
@@ -8396,7 +8393,7 @@
         <v>2026</v>
       </c>
       <c r="C388" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D388" t="s">
         <v>8</v>
@@ -8416,7 +8413,7 @@
         <v>2026</v>
       </c>
       <c r="C389" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D389" t="s">
         <v>8</v>
@@ -8436,7 +8433,7 @@
         <v>2026</v>
       </c>
       <c r="C390" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D390" t="s">
         <v>8</v>
@@ -8456,7 +8453,7 @@
         <v>2026</v>
       </c>
       <c r="C391" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D391" t="s">
         <v>8</v>
@@ -8796,7 +8793,7 @@
         <v>2026</v>
       </c>
       <c r="C408" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D408" t="s">
         <v>8</v>
@@ -8816,7 +8813,7 @@
         <v>2026</v>
       </c>
       <c r="C409" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D409" t="s">
         <v>8</v>
@@ -9676,7 +9673,7 @@
         <v>2026</v>
       </c>
       <c r="C452" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D452" t="s">
         <v>8</v>
@@ -9696,7 +9693,7 @@
         <v>2026</v>
       </c>
       <c r="C453" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D453" t="s">
         <v>8</v>
@@ -9716,7 +9713,7 @@
         <v>2026</v>
       </c>
       <c r="C454" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D454" t="s">
         <v>8</v>
@@ -9736,7 +9733,7 @@
         <v>2026</v>
       </c>
       <c r="C455" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D455" t="s">
         <v>8</v>
@@ -9756,7 +9753,7 @@
         <v>2026</v>
       </c>
       <c r="C456" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D456" t="s">
         <v>8</v>
@@ -9776,7 +9773,7 @@
         <v>2026</v>
       </c>
       <c r="C457" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D457" t="s">
         <v>8</v>
@@ -9796,7 +9793,7 @@
         <v>2026</v>
       </c>
       <c r="C458" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D458" t="s">
         <v>8</v>
@@ -9816,7 +9813,7 @@
         <v>2026</v>
       </c>
       <c r="C459" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D459" t="s">
         <v>8</v>
@@ -9836,7 +9833,7 @@
         <v>2026</v>
       </c>
       <c r="C460" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D460" t="s">
         <v>8</v>
@@ -9856,7 +9853,7 @@
         <v>2026</v>
       </c>
       <c r="C461" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D461" t="s">
         <v>8</v>
@@ -9876,10 +9873,10 @@
         <v>2026</v>
       </c>
       <c r="C462" t="s">
+        <v>34</v>
+      </c>
+      <c r="D462" t="s">
         <v>35</v>
-      </c>
-      <c r="D462" t="s">
-        <v>36</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -9896,10 +9893,10 @@
         <v>2026</v>
       </c>
       <c r="C463" t="s">
+        <v>34</v>
+      </c>
+      <c r="D463" t="s">
         <v>35</v>
-      </c>
-      <c r="D463" t="s">
-        <v>36</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -9916,10 +9913,10 @@
         <v>2026</v>
       </c>
       <c r="C464" t="s">
+        <v>34</v>
+      </c>
+      <c r="D464" t="s">
         <v>35</v>
-      </c>
-      <c r="D464" t="s">
-        <v>36</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -9936,10 +9933,10 @@
         <v>2026</v>
       </c>
       <c r="C465" t="s">
+        <v>34</v>
+      </c>
+      <c r="D465" t="s">
         <v>35</v>
-      </c>
-      <c r="D465" t="s">
-        <v>36</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -9956,10 +9953,10 @@
         <v>2026</v>
       </c>
       <c r="C466" t="s">
+        <v>34</v>
+      </c>
+      <c r="D466" t="s">
         <v>35</v>
-      </c>
-      <c r="D466" t="s">
-        <v>36</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -9976,10 +9973,10 @@
         <v>2026</v>
       </c>
       <c r="C467" t="s">
+        <v>34</v>
+      </c>
+      <c r="D467" t="s">
         <v>35</v>
-      </c>
-      <c r="D467" t="s">
-        <v>36</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -9996,10 +9993,10 @@
         <v>2026</v>
       </c>
       <c r="C468" t="s">
+        <v>34</v>
+      </c>
+      <c r="D468" t="s">
         <v>35</v>
-      </c>
-      <c r="D468" t="s">
-        <v>36</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -10016,10 +10013,10 @@
         <v>2026</v>
       </c>
       <c r="C469" t="s">
+        <v>34</v>
+      </c>
+      <c r="D469" t="s">
         <v>35</v>
-      </c>
-      <c r="D469" t="s">
-        <v>36</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -10036,10 +10033,10 @@
         <v>2026</v>
       </c>
       <c r="C470" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D470" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -10056,10 +10053,10 @@
         <v>2026</v>
       </c>
       <c r="C471" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D471" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -10076,10 +10073,10 @@
         <v>2026</v>
       </c>
       <c r="C472" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D472" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -10096,10 +10093,10 @@
         <v>2026</v>
       </c>
       <c r="C473" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D473" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -10116,10 +10113,10 @@
         <v>2026</v>
       </c>
       <c r="C474" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D474" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -10136,10 +10133,10 @@
         <v>2026</v>
       </c>
       <c r="C475" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D475" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -10156,10 +10153,10 @@
         <v>2026</v>
       </c>
       <c r="C476" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D476" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -10176,10 +10173,10 @@
         <v>2026</v>
       </c>
       <c r="C477" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D477" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -10196,10 +10193,10 @@
         <v>2026</v>
       </c>
       <c r="C478" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D478" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E478" t="s">
         <v>9</v>
@@ -10216,10 +10213,10 @@
         <v>2026</v>
       </c>
       <c r="C479" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D479" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E479" t="s">
         <v>9</v>
@@ -10236,10 +10233,10 @@
         <v>2026</v>
       </c>
       <c r="C480" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D480" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E480" t="s">
         <v>9</v>
@@ -10256,10 +10253,10 @@
         <v>2026</v>
       </c>
       <c r="C481" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D481" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E481" t="s">
         <v>9</v>
@@ -10276,10 +10273,10 @@
         <v>2026</v>
       </c>
       <c r="C482" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D482" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E482" t="s">
         <v>9</v>
@@ -10296,10 +10293,10 @@
         <v>2026</v>
       </c>
       <c r="C483" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D483" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E483" t="s">
         <v>9</v>
@@ -10316,10 +10313,10 @@
         <v>2026</v>
       </c>
       <c r="C484" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D484" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E484" t="s">
         <v>9</v>
@@ -10336,10 +10333,10 @@
         <v>2026</v>
       </c>
       <c r="C485" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D485" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E485" t="s">
         <v>9</v>
@@ -10356,13 +10353,13 @@
         <v>2026</v>
       </c>
       <c r="C486" t="s">
+        <v>38</v>
+      </c>
+      <c r="D486" t="s">
         <v>39</v>
       </c>
-      <c r="D486" t="s">
-        <v>40</v>
-      </c>
       <c r="E486" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F486">
         <v>832</v>
@@ -10376,13 +10373,13 @@
         <v>2026</v>
       </c>
       <c r="C487" t="s">
+        <v>38</v>
+      </c>
+      <c r="D487" t="s">
         <v>39</v>
       </c>
-      <c r="D487" t="s">
-        <v>40</v>
-      </c>
       <c r="E487" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F487">
         <v>1560</v>
@@ -10396,13 +10393,13 @@
         <v>2026</v>
       </c>
       <c r="C488" t="s">
+        <v>38</v>
+      </c>
+      <c r="D488" t="s">
         <v>39</v>
       </c>
-      <c r="D488" t="s">
-        <v>40</v>
-      </c>
       <c r="E488" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F488">
         <v>1560</v>
@@ -10416,13 +10413,13 @@
         <v>2026</v>
       </c>
       <c r="C489" t="s">
+        <v>38</v>
+      </c>
+      <c r="D489" t="s">
         <v>39</v>
       </c>
-      <c r="D489" t="s">
-        <v>40</v>
-      </c>
       <c r="E489" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F489">
         <v>1560</v>
@@ -10436,13 +10433,13 @@
         <v>2026</v>
       </c>
       <c r="C490" t="s">
+        <v>38</v>
+      </c>
+      <c r="D490" t="s">
         <v>39</v>
       </c>
-      <c r="D490" t="s">
-        <v>40</v>
-      </c>
       <c r="E490" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F490">
         <v>1560</v>
@@ -10456,13 +10453,13 @@
         <v>2026</v>
       </c>
       <c r="C491" t="s">
+        <v>38</v>
+      </c>
+      <c r="D491" t="s">
         <v>39</v>
       </c>
-      <c r="D491" t="s">
-        <v>40</v>
-      </c>
       <c r="E491" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F491">
         <v>1560</v>
@@ -10476,13 +10473,13 @@
         <v>2026</v>
       </c>
       <c r="C492" t="s">
+        <v>38</v>
+      </c>
+      <c r="D492" t="s">
         <v>39</v>
       </c>
-      <c r="D492" t="s">
-        <v>40</v>
-      </c>
       <c r="E492" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F492">
         <v>1560</v>
@@ -10496,13 +10493,13 @@
         <v>2026</v>
       </c>
       <c r="C493" t="s">
+        <v>38</v>
+      </c>
+      <c r="D493" t="s">
         <v>39</v>
       </c>
-      <c r="D493" t="s">
-        <v>40</v>
-      </c>
       <c r="E493" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F493">
         <v>1560</v>
@@ -10516,13 +10513,13 @@
         <v>2026</v>
       </c>
       <c r="C494" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D494" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E494" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F494">
         <v>3469</v>
@@ -10536,13 +10533,13 @@
         <v>2026</v>
       </c>
       <c r="C495" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D495" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E495" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F495">
         <v>3577</v>
@@ -10556,13 +10553,13 @@
         <v>2026</v>
       </c>
       <c r="C496" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D496" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E496" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F496">
         <v>3535</v>
@@ -10576,13 +10573,13 @@
         <v>2026</v>
       </c>
       <c r="C497" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D497" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E497" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F497">
         <v>3627</v>
@@ -10596,13 +10593,13 @@
         <v>2026</v>
       </c>
       <c r="C498" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D498" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E498" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F498">
         <v>3640</v>
@@ -10616,13 +10613,13 @@
         <v>2026</v>
       </c>
       <c r="C499" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D499" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E499" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F499">
         <v>3469</v>
@@ -10636,13 +10633,13 @@
         <v>2026</v>
       </c>
       <c r="C500" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D500" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E500" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F500">
         <v>3571</v>
@@ -10656,13 +10653,13 @@
         <v>2026</v>
       </c>
       <c r="C501" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D501" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E501" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F501">
         <v>3550</v>
@@ -10676,13 +10673,13 @@
         <v>2026</v>
       </c>
       <c r="C502" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D502" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E502" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F502">
         <v>443</v>
@@ -10696,13 +10693,13 @@
         <v>2026</v>
       </c>
       <c r="C503" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D503" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E503" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F503">
         <v>280</v>
@@ -10716,13 +10713,13 @@
         <v>2026</v>
       </c>
       <c r="C504" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D504" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E504" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F504">
         <v>0</v>
@@ -10736,13 +10733,13 @@
         <v>2026</v>
       </c>
       <c r="C505" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D505" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E505" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F505">
         <v>533</v>
@@ -10756,13 +10753,13 @@
         <v>2026</v>
       </c>
       <c r="C506" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D506" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E506" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F506">
         <v>45</v>
@@ -10776,13 +10773,13 @@
         <v>2026</v>
       </c>
       <c r="C507" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D507" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E507" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F507">
         <v>485</v>
@@ -10796,13 +10793,13 @@
         <v>2026</v>
       </c>
       <c r="C508" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D508" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E508" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F508">
         <v>553</v>
@@ -10816,13 +10813,13 @@
         <v>2026</v>
       </c>
       <c r="C509" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D509" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E509" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F509">
         <v>465</v>
@@ -10836,13 +10833,13 @@
         <v>2026</v>
       </c>
       <c r="C510" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D510" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E510" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F510">
         <v>325</v>
@@ -10856,13 +10853,13 @@
         <v>2026</v>
       </c>
       <c r="C511" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D511" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E511" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F511">
         <v>488</v>
@@ -10876,13 +10873,13 @@
         <v>2026</v>
       </c>
       <c r="C512" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D512" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E512" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F512">
         <v>235</v>
@@ -10896,13 +10893,13 @@
         <v>2026</v>
       </c>
       <c r="C513" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D513" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E513" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F513">
         <v>90</v>
@@ -10916,13 +10913,13 @@
         <v>2026</v>
       </c>
       <c r="C514" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D514" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E514" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F514">
         <v>395</v>
@@ -10936,13 +10933,13 @@
         <v>2026</v>
       </c>
       <c r="C515" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D515" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E515" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F515">
         <v>448</v>
@@ -10956,13 +10953,13 @@
         <v>2026</v>
       </c>
       <c r="C516" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D516" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E516" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F516">
         <v>60</v>
@@ -10976,13 +10973,13 @@
         <v>2026</v>
       </c>
       <c r="C517" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D517" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E517" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F517">
         <v>433</v>
@@ -10996,13 +10993,13 @@
         <v>2026</v>
       </c>
       <c r="C518" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D518" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E518" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F518">
         <v>445</v>
@@ -11016,13 +11013,13 @@
         <v>2026</v>
       </c>
       <c r="C519" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D519" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E519" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F519">
         <v>103</v>
@@ -11036,13 +11033,13 @@
         <v>2026</v>
       </c>
       <c r="C520" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D520" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E520" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F520">
         <v>183</v>
@@ -11056,13 +11053,13 @@
         <v>2026</v>
       </c>
       <c r="C521" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D521" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E521" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F521">
         <v>95</v>
@@ -11076,13 +11073,13 @@
         <v>2026</v>
       </c>
       <c r="C522" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D522" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E522" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F522">
         <v>223</v>
@@ -11096,13 +11093,13 @@
         <v>2026</v>
       </c>
       <c r="C523" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D523" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E523" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F523">
         <v>385</v>
@@ -11116,13 +11113,13 @@
         <v>2026</v>
       </c>
       <c r="C524" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D524" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E524" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F524">
         <v>120</v>
@@ -11136,13 +11133,13 @@
         <v>2026</v>
       </c>
       <c r="C525" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D525" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E525" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F525">
         <v>50</v>
@@ -11156,13 +11153,13 @@
         <v>2026</v>
       </c>
       <c r="C526" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D526" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E526" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F526">
         <v>0</v>
@@ -11176,13 +11173,13 @@
         <v>2026</v>
       </c>
       <c r="C527" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D527" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E527" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F527">
         <v>340</v>
@@ -11196,13 +11193,13 @@
         <v>2026</v>
       </c>
       <c r="C528" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D528" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E528" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F528">
         <v>30</v>
@@ -11216,13 +11213,13 @@
         <v>2026</v>
       </c>
       <c r="C529" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D529" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E529" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F529">
         <v>190</v>
@@ -11236,13 +11233,13 @@
         <v>2026</v>
       </c>
       <c r="C530" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D530" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E530" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F530">
         <v>0</v>
@@ -11256,13 +11253,13 @@
         <v>2026</v>
       </c>
       <c r="C531" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D531" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E531" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F531">
         <v>100</v>
@@ -11276,13 +11273,13 @@
         <v>2026</v>
       </c>
       <c r="C532" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D532" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E532" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F532">
         <v>391</v>
@@ -11296,13 +11293,13 @@
         <v>2026</v>
       </c>
       <c r="C533" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D533" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E533" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F533">
         <v>203</v>
@@ -11316,13 +11313,13 @@
         <v>2026</v>
       </c>
       <c r="C534" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D534" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E534" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F534">
         <v>960</v>
@@ -11336,13 +11333,13 @@
         <v>2026</v>
       </c>
       <c r="C535" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D535" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E535" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F535">
         <v>253</v>
@@ -11356,13 +11353,13 @@
         <v>2026</v>
       </c>
       <c r="C536" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D536" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E536" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F536">
         <v>143</v>
@@ -11376,13 +11373,13 @@
         <v>2026</v>
       </c>
       <c r="C537" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D537" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E537" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F537">
         <v>209</v>
@@ -11396,13 +11393,13 @@
         <v>2026</v>
       </c>
       <c r="C538" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D538" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E538" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F538">
         <v>610</v>
@@ -11416,13 +11413,13 @@
         <v>2026</v>
       </c>
       <c r="C539" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D539" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E539" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F539">
         <v>1558</v>
@@ -11436,13 +11433,13 @@
         <v>2026</v>
       </c>
       <c r="C540" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D540" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E540" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F540">
         <v>1698</v>
@@ -11456,13 +11453,13 @@
         <v>2026</v>
       </c>
       <c r="C541" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D541" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E541" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F541">
         <v>1533</v>
@@ -11476,13 +11473,13 @@
         <v>2026</v>
       </c>
       <c r="C542" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D542" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E542" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F542">
         <v>1176</v>
@@ -11496,13 +11493,13 @@
         <v>2026</v>
       </c>
       <c r="C543" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D543" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E543" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F543">
         <v>559</v>
@@ -11516,13 +11513,13 @@
         <v>2026</v>
       </c>
       <c r="C544" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D544" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E544" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F544">
         <v>1511</v>
@@ -11536,13 +11533,13 @@
         <v>2026</v>
       </c>
       <c r="C545" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D545" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E545" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F545">
         <v>2069</v>
@@ -11556,13 +11553,13 @@
         <v>2026</v>
       </c>
       <c r="C546" t="s">
+        <v>48</v>
+      </c>
+      <c r="D546" t="s">
+        <v>43</v>
+      </c>
+      <c r="E546" t="s">
         <v>49</v>
-      </c>
-      <c r="D546" t="s">
-        <v>44</v>
-      </c>
-      <c r="E546" t="s">
-        <v>50</v>
       </c>
       <c r="F546">
         <v>544</v>
@@ -11576,13 +11573,13 @@
         <v>2026</v>
       </c>
       <c r="C547" t="s">
+        <v>48</v>
+      </c>
+      <c r="D547" t="s">
+        <v>43</v>
+      </c>
+      <c r="E547" t="s">
         <v>49</v>
-      </c>
-      <c r="D547" t="s">
-        <v>44</v>
-      </c>
-      <c r="E547" t="s">
-        <v>50</v>
       </c>
       <c r="F547">
         <v>3321</v>
@@ -11596,13 +11593,13 @@
         <v>2026</v>
       </c>
       <c r="C548" t="s">
+        <v>48</v>
+      </c>
+      <c r="D548" t="s">
+        <v>43</v>
+      </c>
+      <c r="E548" t="s">
         <v>49</v>
-      </c>
-      <c r="D548" t="s">
-        <v>44</v>
-      </c>
-      <c r="E548" t="s">
-        <v>50</v>
       </c>
       <c r="F548">
         <v>1960</v>
@@ -11616,13 +11613,13 @@
         <v>2026</v>
       </c>
       <c r="C549" t="s">
+        <v>48</v>
+      </c>
+      <c r="D549" t="s">
+        <v>43</v>
+      </c>
+      <c r="E549" t="s">
         <v>49</v>
-      </c>
-      <c r="D549" t="s">
-        <v>44</v>
-      </c>
-      <c r="E549" t="s">
-        <v>50</v>
       </c>
       <c r="F549">
         <v>2468</v>
@@ -11636,13 +11633,13 @@
         <v>2026</v>
       </c>
       <c r="C550" t="s">
+        <v>48</v>
+      </c>
+      <c r="D550" t="s">
+        <v>43</v>
+      </c>
+      <c r="E550" t="s">
         <v>49</v>
-      </c>
-      <c r="D550" t="s">
-        <v>44</v>
-      </c>
-      <c r="E550" t="s">
-        <v>50</v>
       </c>
       <c r="F550">
         <v>1737</v>
@@ -11656,13 +11653,13 @@
         <v>2026</v>
       </c>
       <c r="C551" t="s">
+        <v>48</v>
+      </c>
+      <c r="D551" t="s">
+        <v>43</v>
+      </c>
+      <c r="E551" t="s">
         <v>49</v>
-      </c>
-      <c r="D551" t="s">
-        <v>44</v>
-      </c>
-      <c r="E551" t="s">
-        <v>50</v>
       </c>
       <c r="F551">
         <v>986</v>
@@ -11676,13 +11673,13 @@
         <v>2026</v>
       </c>
       <c r="C552" t="s">
+        <v>48</v>
+      </c>
+      <c r="D552" t="s">
+        <v>43</v>
+      </c>
+      <c r="E552" t="s">
         <v>49</v>
-      </c>
-      <c r="D552" t="s">
-        <v>44</v>
-      </c>
-      <c r="E552" t="s">
-        <v>50</v>
       </c>
       <c r="F552">
         <v>1860</v>
@@ -11696,13 +11693,13 @@
         <v>2026</v>
       </c>
       <c r="C553" t="s">
+        <v>48</v>
+      </c>
+      <c r="D553" t="s">
+        <v>43</v>
+      </c>
+      <c r="E553" t="s">
         <v>49</v>
-      </c>
-      <c r="D553" t="s">
-        <v>44</v>
-      </c>
-      <c r="E553" t="s">
-        <v>50</v>
       </c>
       <c r="F553">
         <v>2489</v>
@@ -11716,13 +11713,13 @@
         <v>2026</v>
       </c>
       <c r="C554" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D554" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E554" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F554">
         <v>820</v>
@@ -11736,13 +11733,13 @@
         <v>2026</v>
       </c>
       <c r="C555" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D555" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E555" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F555">
         <v>1388</v>
@@ -11756,13 +11753,13 @@
         <v>2026</v>
       </c>
       <c r="C556" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D556" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E556" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F556">
         <v>1088</v>
@@ -11776,13 +11773,13 @@
         <v>2026</v>
       </c>
       <c r="C557" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D557" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E557" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F557">
         <v>480</v>
@@ -11796,13 +11793,13 @@
         <v>2026</v>
       </c>
       <c r="C558" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D558" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E558" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F558">
         <v>1158</v>
@@ -11816,13 +11813,13 @@
         <v>2026</v>
       </c>
       <c r="C559" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D559" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E559" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F559">
         <v>1460</v>
@@ -11836,13 +11833,13 @@
         <v>2026</v>
       </c>
       <c r="C560" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D560" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E560" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F560">
         <v>346</v>
@@ -11856,13 +11853,13 @@
         <v>2026</v>
       </c>
       <c r="C561" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D561" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E561" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F561">
         <v>1266</v>
@@ -11876,13 +11873,13 @@
         <v>2026</v>
       </c>
       <c r="C562" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D562" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E562" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F562">
         <v>1360</v>
@@ -11896,13 +11893,13 @@
         <v>2026</v>
       </c>
       <c r="C563" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D563" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E563" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F563">
         <v>1948</v>
@@ -11916,13 +11913,13 @@
         <v>2026</v>
       </c>
       <c r="C564" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D564" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E564" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F564">
         <v>790</v>
@@ -11936,13 +11933,13 @@
         <v>2026</v>
       </c>
       <c r="C565" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D565" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E565" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F565">
         <v>592</v>
@@ -11956,13 +11953,13 @@
         <v>2026</v>
       </c>
       <c r="C566" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D566" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E566" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F566">
         <v>1489</v>
@@ -11976,13 +11973,13 @@
         <v>2026</v>
       </c>
       <c r="C567" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D567" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E567" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F567">
         <v>1643</v>
@@ -11996,13 +11993,13 @@
         <v>2026</v>
       </c>
       <c r="C568" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D568" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E568" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F568">
         <v>313</v>
@@ -12016,13 +12013,13 @@
         <v>2026</v>
       </c>
       <c r="C569" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D569" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E569" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F569">
         <v>1059</v>
@@ -12036,13 +12033,13 @@
         <v>2026</v>
       </c>
       <c r="C570" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D570" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E570" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F570">
         <v>741</v>
@@ -12056,13 +12053,13 @@
         <v>2026</v>
       </c>
       <c r="C571" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D571" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E571" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F571">
         <v>558</v>
@@ -12076,13 +12073,13 @@
         <v>2026</v>
       </c>
       <c r="C572" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D572" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E572" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F572">
         <v>1418</v>
@@ -12096,13 +12093,13 @@
         <v>2026</v>
       </c>
       <c r="C573" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D573" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E573" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F573">
         <v>355</v>
@@ -12116,13 +12113,13 @@
         <v>2026</v>
       </c>
       <c r="C574" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D574" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E574" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F574">
         <v>324</v>
@@ -12136,13 +12133,13 @@
         <v>2026</v>
       </c>
       <c r="C575" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D575" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E575" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F575">
         <v>762</v>
@@ -12156,13 +12153,13 @@
         <v>2026</v>
       </c>
       <c r="C576" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D576" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E576" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F576">
         <v>315</v>
@@ -12176,13 +12173,13 @@
         <v>2026</v>
       </c>
       <c r="C577" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D577" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E577" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F577">
         <v>470</v>
@@ -12196,13 +12193,13 @@
         <v>2026</v>
       </c>
       <c r="C578" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D578" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E578" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F578">
         <v>783</v>
@@ -12216,13 +12213,13 @@
         <v>2026</v>
       </c>
       <c r="C579" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D579" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E579" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F579">
         <v>300</v>
@@ -12236,13 +12233,13 @@
         <v>2026</v>
       </c>
       <c r="C580" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D580" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E580" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F580">
         <v>508</v>
@@ -12256,13 +12253,13 @@
         <v>2026</v>
       </c>
       <c r="C581" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D581" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E581" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F581">
         <v>553</v>
@@ -12279,10 +12276,10 @@
         <v>30</v>
       </c>
       <c r="D582" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E582" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F582">
         <v>1626</v>
@@ -12299,10 +12296,10 @@
         <v>30</v>
       </c>
       <c r="D583" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E583" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F583">
         <v>1853</v>
@@ -12319,10 +12316,10 @@
         <v>30</v>
       </c>
       <c r="D584" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E584" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F584">
         <v>1805</v>
@@ -12339,10 +12336,10 @@
         <v>30</v>
       </c>
       <c r="D585" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E585" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F585">
         <v>710</v>
@@ -12359,10 +12356,10 @@
         <v>30</v>
       </c>
       <c r="D586" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E586" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F586">
         <v>1612</v>
@@ -12379,10 +12376,10 @@
         <v>30</v>
       </c>
       <c r="D587" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E587" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F587">
         <v>2601</v>
@@ -12396,13 +12393,13 @@
         <v>2026</v>
       </c>
       <c r="C588" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D588" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E588" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F588">
         <v>1941</v>
@@ -12416,13 +12413,13 @@
         <v>2026</v>
       </c>
       <c r="C589" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D589" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E589" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F589">
         <v>1815</v>
@@ -12436,13 +12433,13 @@
         <v>2026</v>
       </c>
       <c r="C590" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D590" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E590" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F590">
         <v>2140</v>
@@ -12456,13 +12453,13 @@
         <v>2026</v>
       </c>
       <c r="C591" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D591" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E591" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F591">
         <v>1185</v>
@@ -12476,13 +12473,13 @@
         <v>2026</v>
       </c>
       <c r="C592" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D592" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E592" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F592">
         <v>121</v>
@@ -12496,13 +12493,13 @@
         <v>2026</v>
       </c>
       <c r="C593" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D593" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E593" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F593">
         <v>1678</v>
@@ -12516,13 +12513,13 @@
         <v>2026</v>
       </c>
       <c r="C594" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D594" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E594" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F594">
         <v>2243</v>
@@ -12536,13 +12533,13 @@
         <v>2026</v>
       </c>
       <c r="C595" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D595" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E595" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F595">
         <v>1791</v>
@@ -12556,13 +12553,13 @@
         <v>2026</v>
       </c>
       <c r="C596" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D596" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E596" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F596">
         <v>1611</v>
@@ -12576,13 +12573,13 @@
         <v>2026</v>
       </c>
       <c r="C597" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D597" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E597" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F597">
         <v>1500</v>
@@ -12596,13 +12593,13 @@
         <v>2026</v>
       </c>
       <c r="C598" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D598" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E598" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F598">
         <v>1650</v>
@@ -12616,13 +12613,13 @@
         <v>2026</v>
       </c>
       <c r="C599" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D599" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E599" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F599">
         <v>1645</v>
@@ -12636,13 +12633,13 @@
         <v>2026</v>
       </c>
       <c r="C600" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D600" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E600" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F600">
         <v>1500</v>
@@ -12656,13 +12653,13 @@
         <v>2026</v>
       </c>
       <c r="C601" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D601" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E601" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F601">
         <v>1645</v>
@@ -12676,13 +12673,13 @@
         <v>2026</v>
       </c>
       <c r="C602" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D602" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E602" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F602">
         <v>3291</v>
@@ -12696,13 +12693,13 @@
         <v>2026</v>
       </c>
       <c r="C603" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D603" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E603" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F603">
         <v>1500</v>
@@ -12716,13 +12713,13 @@
         <v>2026</v>
       </c>
       <c r="C604" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D604" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E604" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F604">
         <v>449</v>
@@ -12736,13 +12733,13 @@
         <v>2026</v>
       </c>
       <c r="C605" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D605" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E605" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F605">
         <v>120</v>
@@ -12756,13 +12753,13 @@
         <v>2026</v>
       </c>
       <c r="C606" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D606" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E606" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F606">
         <v>530</v>
@@ -12776,13 +12773,13 @@
         <v>2026</v>
       </c>
       <c r="C607" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D607" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E607" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F607">
         <v>130</v>
@@ -12796,13 +12793,13 @@
         <v>2026</v>
       </c>
       <c r="C608" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D608" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E608" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F608">
         <v>195</v>
@@ -12816,13 +12813,13 @@
         <v>2026</v>
       </c>
       <c r="C609" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D609" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E609" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F609">
         <v>285</v>
@@ -12836,13 +12833,13 @@
         <v>2026</v>
       </c>
       <c r="C610" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D610" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E610" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F610">
         <v>405</v>
@@ -12856,13 +12853,13 @@
         <v>2026</v>
       </c>
       <c r="C611" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D611" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E611" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F611">
         <v>335</v>
@@ -12876,13 +12873,13 @@
         <v>2026</v>
       </c>
       <c r="C612" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D612" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E612" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F612">
         <v>270</v>
@@ -12896,13 +12893,13 @@
         <v>2026</v>
       </c>
       <c r="C613" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D613" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E613" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F613">
         <v>75</v>
@@ -12916,13 +12913,13 @@
         <v>2026</v>
       </c>
       <c r="C614" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D614" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E614" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F614">
         <v>275</v>
@@ -12936,13 +12933,13 @@
         <v>2026</v>
       </c>
       <c r="C615" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D615" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E615" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F615">
         <v>218</v>
@@ -12956,13 +12953,13 @@
         <v>2026</v>
       </c>
       <c r="C616" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D616" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E616" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F616">
         <v>49</v>
@@ -12976,13 +12973,13 @@
         <v>2026</v>
       </c>
       <c r="C617" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D617" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E617" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F617">
         <v>1459</v>
@@ -12996,13 +12993,13 @@
         <v>2026</v>
       </c>
       <c r="C618" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D618" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E618" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F618">
         <v>1241</v>
@@ -13016,13 +13013,13 @@
         <v>2026</v>
       </c>
       <c r="C619" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D619" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E619" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F619">
         <v>2019</v>
@@ -13036,13 +13033,13 @@
         <v>2026</v>
       </c>
       <c r="C620" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D620" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E620" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F620">
         <v>1172</v>
@@ -13056,13 +13053,13 @@
         <v>2026</v>
       </c>
       <c r="C621" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D621" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E621" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F621">
         <v>97</v>
@@ -13076,13 +13073,13 @@
         <v>2026</v>
       </c>
       <c r="C622" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D622" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E622" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F622">
         <v>1611</v>
@@ -13096,13 +13093,13 @@
         <v>2026</v>
       </c>
       <c r="C623" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D623" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E623" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F623">
         <v>575</v>
@@ -13116,13 +13113,13 @@
         <v>2026</v>
       </c>
       <c r="C624" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D624" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E624" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F624">
         <v>1055</v>
@@ -13136,13 +13133,13 @@
         <v>2026</v>
       </c>
       <c r="C625" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D625" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E625" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F625">
         <v>1260</v>
@@ -13156,13 +13153,13 @@
         <v>2026</v>
       </c>
       <c r="C626" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D626" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E626" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F626">
         <v>1130</v>
@@ -13176,13 +13173,13 @@
         <v>2026</v>
       </c>
       <c r="C627" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D627" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E627" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F627">
         <v>864</v>
@@ -13196,13 +13193,13 @@
         <v>2026</v>
       </c>
       <c r="C628" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D628" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E628" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F628">
         <v>868</v>
@@ -13216,13 +13213,13 @@
         <v>2026</v>
       </c>
       <c r="C629" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D629" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E629" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F629">
         <v>1118</v>
@@ -13236,13 +13233,13 @@
         <v>2026</v>
       </c>
       <c r="C630" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D630" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E630" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F630">
         <v>1386</v>
@@ -13256,13 +13253,13 @@
         <v>2026</v>
       </c>
       <c r="C631" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D631" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E631" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F631">
         <v>235</v>
@@ -13276,13 +13273,13 @@
         <v>2026</v>
       </c>
       <c r="C632" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D632" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E632" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F632">
         <v>501</v>
@@ -13296,13 +13293,13 @@
         <v>2026</v>
       </c>
       <c r="C633" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D633" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E633" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F633">
         <v>165</v>
@@ -13316,13 +13313,13 @@
         <v>2026</v>
       </c>
       <c r="C634" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D634" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E634" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F634">
         <v>458</v>
@@ -13336,13 +13333,13 @@
         <v>2026</v>
       </c>
       <c r="C635" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D635" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E635" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F635">
         <v>360</v>
@@ -13356,13 +13353,13 @@
         <v>2026</v>
       </c>
       <c r="C636" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D636" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E636" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F636">
         <v>140</v>
@@ -13376,13 +13373,13 @@
         <v>2026</v>
       </c>
       <c r="C637" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D637" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E637" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F637">
         <v>165</v>
@@ -13396,13 +13393,13 @@
         <v>2026</v>
       </c>
       <c r="C638" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D638" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E638" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F638">
         <v>818</v>
@@ -13416,13 +13413,13 @@
         <v>2026</v>
       </c>
       <c r="C639" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D639" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E639" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F639">
         <v>300</v>
@@ -13436,13 +13433,13 @@
         <v>2026</v>
       </c>
       <c r="C640" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D640" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E640" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F640">
         <v>315</v>
@@ -13456,13 +13453,13 @@
         <v>2026</v>
       </c>
       <c r="C641" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D641" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E641" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F641">
         <v>143</v>
@@ -13476,13 +13473,13 @@
         <v>2026</v>
       </c>
       <c r="C642" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D642" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E642" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F642">
         <v>60</v>
@@ -13496,13 +13493,13 @@
         <v>2026</v>
       </c>
       <c r="C643" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D643" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E643" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F643">
         <v>360</v>
@@ -13516,13 +13513,13 @@
         <v>2026</v>
       </c>
       <c r="C644" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D644" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E644" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F644">
         <v>305</v>
@@ -13536,13 +13533,13 @@
         <v>2026</v>
       </c>
       <c r="C645" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D645" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E645" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F645">
         <v>60</v>
@@ -13556,13 +13553,13 @@
         <v>2026</v>
       </c>
       <c r="C646" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D646" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E646" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F646">
         <v>60</v>
@@ -13576,13 +13573,13 @@
         <v>2026</v>
       </c>
       <c r="C647" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D647" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E647" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F647">
         <v>150</v>
@@ -13596,13 +13593,13 @@
         <v>2026</v>
       </c>
       <c r="C648" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D648" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E648" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F648">
         <v>668</v>
@@ -13616,13 +13613,13 @@
         <v>2026</v>
       </c>
       <c r="C649" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D649" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E649" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F649">
         <v>282</v>
@@ -13636,13 +13633,13 @@
         <v>2026</v>
       </c>
       <c r="C650" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D650" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E650" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F650">
         <v>205</v>
@@ -13656,13 +13653,13 @@
         <v>2026</v>
       </c>
       <c r="C651" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D651" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E651" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F651">
         <v>340</v>
@@ -13676,13 +13673,13 @@
         <v>2026</v>
       </c>
       <c r="C652" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D652" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E652" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F652">
         <v>528</v>

--- a/DASHBOARD COSTO LAVORO 2025-2026.xlsx
+++ b/DASHBOARD COSTO LAVORO 2025-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\dpiccoli\Kundalini Unipersonale\Collaboratori\DASH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9503CC42-0AA2-4588-B965-3C7CE1502C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4701C41-D22F-4BD3-A97D-7BA493D81473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="17400" xr2:uid="{0E1E5C30-1EA2-40EC-BCF7-60B4522243F2}"/>
   </bookViews>
@@ -155,9 +155,6 @@
     <t>MORANDI PAOLO</t>
   </si>
   <si>
-    <t>ANTONIO ZECCHINO</t>
-  </si>
-  <si>
     <t>PROFESSIONISTA</t>
   </si>
   <si>
@@ -270,6 +267,9 @@
   </si>
   <si>
     <t>BAR MANAGER</t>
+  </si>
+  <si>
+    <t>ZECCHINO ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -723,13 +723,13 @@
         <v>2025</v>
       </c>
       <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>1456</v>
@@ -749,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4">
         <v>616</v>
@@ -829,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8">
         <v>876</v>
@@ -843,13 +843,13 @@
         <v>2025</v>
       </c>
       <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
         <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>49</v>
       </c>
       <c r="F9">
         <v>424</v>
@@ -863,13 +863,13 @@
         <v>2025</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10">
         <v>349</v>
@@ -903,13 +903,13 @@
         <v>2025</v>
       </c>
       <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
         <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
       </c>
       <c r="F12">
         <v>378</v>
@@ -929,7 +929,7 @@
         <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13">
         <v>1973</v>
@@ -943,13 +943,13 @@
         <v>2025</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14">
         <v>3333</v>
@@ -1026,10 +1026,10 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18">
         <v>146</v>
@@ -1049,7 +1049,7 @@
         <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19">
         <v>4008</v>
@@ -1063,13 +1063,13 @@
         <v>2025</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20">
         <v>1645</v>
@@ -1123,13 +1123,13 @@
         <v>2025</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23">
         <v>1375</v>
@@ -1143,13 +1143,13 @@
         <v>2025</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24">
         <v>646</v>
@@ -1163,13 +1163,13 @@
         <v>2025</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25">
         <v>378</v>
@@ -1203,13 +1203,13 @@
         <v>2026</v>
       </c>
       <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
         <v>38</v>
       </c>
-      <c r="D27" t="s">
-        <v>39</v>
-      </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27">
         <v>832</v>
@@ -1223,7 +1223,7 @@
         <v>2026</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
@@ -1249,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29">
         <v>707</v>
@@ -1283,13 +1283,13 @@
         <v>2026</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F31">
         <v>60</v>
@@ -1303,13 +1303,13 @@
         <v>2026</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F32">
         <v>120</v>
@@ -1323,7 +1323,7 @@
         <v>2026</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35">
         <v>1435</v>
@@ -1383,13 +1383,13 @@
         <v>2026</v>
       </c>
       <c r="C36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" t="s">
         <v>48</v>
-      </c>
-      <c r="D36" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" t="s">
-        <v>49</v>
       </c>
       <c r="F36">
         <v>544</v>
@@ -1403,13 +1403,13 @@
         <v>2026</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37">
         <v>346</v>
@@ -1443,13 +1443,13 @@
         <v>2026</v>
       </c>
       <c r="C39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" t="s">
         <v>52</v>
-      </c>
-      <c r="D39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E39" t="s">
-        <v>53</v>
       </c>
       <c r="F39">
         <v>313</v>
@@ -1469,7 +1469,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F40">
         <v>2273</v>
@@ -1483,13 +1483,13 @@
         <v>2026</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41">
         <v>3469</v>
@@ -1549,7 +1549,7 @@
         <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44">
         <v>3472</v>
@@ -1563,13 +1563,13 @@
         <v>2026</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>1791</v>
@@ -1583,13 +1583,13 @@
         <v>2026</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F46">
         <v>1375</v>
@@ -1603,13 +1603,13 @@
         <v>2026</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F47">
         <v>49</v>
@@ -1623,13 +1623,13 @@
         <v>2026</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48">
         <v>868</v>
@@ -1643,13 +1643,13 @@
         <v>2026</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F49">
         <v>235</v>
@@ -1663,13 +1663,13 @@
         <v>2026</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F50">
         <v>60</v>
@@ -1703,13 +1703,13 @@
         <v>2025</v>
       </c>
       <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
         <v>38</v>
       </c>
-      <c r="D52" t="s">
-        <v>39</v>
-      </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F52">
         <v>1820</v>
@@ -1729,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53">
         <v>1481</v>
@@ -1743,13 +1743,13 @@
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F54">
         <v>181</v>
@@ -1763,13 +1763,13 @@
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F55">
         <v>331</v>
@@ -1803,13 +1803,13 @@
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F57">
         <v>471</v>
@@ -1823,13 +1823,13 @@
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F58">
         <v>1679</v>
@@ -1849,7 +1849,7 @@
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F59">
         <v>1240</v>
@@ -1863,13 +1863,13 @@
         <v>2025</v>
       </c>
       <c r="C60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" t="s">
         <v>48</v>
-      </c>
-      <c r="D60" t="s">
-        <v>43</v>
-      </c>
-      <c r="E60" t="s">
-        <v>49</v>
       </c>
       <c r="F60">
         <v>1391</v>
@@ -1883,13 +1883,13 @@
         <v>2025</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F61">
         <v>2118</v>
@@ -1923,13 +1923,13 @@
         <v>2025</v>
       </c>
       <c r="C63" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" t="s">
         <v>52</v>
-      </c>
-      <c r="D63" t="s">
-        <v>43</v>
-      </c>
-      <c r="E63" t="s">
-        <v>53</v>
       </c>
       <c r="F63">
         <v>546</v>
@@ -1949,7 +1949,7 @@
         <v>35</v>
       </c>
       <c r="E64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F64">
         <v>3517</v>
@@ -1963,13 +1963,13 @@
         <v>2025</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F65">
         <v>3333</v>
@@ -1983,13 +1983,13 @@
         <v>2025</v>
       </c>
       <c r="C66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F66">
         <v>278</v>
@@ -2003,13 +2003,13 @@
         <v>2025</v>
       </c>
       <c r="C67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F67">
         <v>511</v>
@@ -2066,10 +2066,10 @@
         <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F70">
         <v>362</v>
@@ -2083,13 +2083,13 @@
         <v>2025</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F71">
         <v>2065</v>
@@ -2109,7 +2109,7 @@
         <v>35</v>
       </c>
       <c r="E72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F72">
         <v>3924</v>
@@ -2123,13 +2123,13 @@
         <v>2025</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E73" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F73">
         <v>1597</v>
@@ -2163,13 +2163,13 @@
         <v>2025</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F75">
         <v>270</v>
@@ -2183,13 +2183,13 @@
         <v>2025</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D76" t="s">
         <v>8</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F76">
         <v>1327</v>
@@ -2223,13 +2223,13 @@
         <v>2025</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F78">
         <v>1333</v>
@@ -2243,13 +2243,13 @@
         <v>2025</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F79">
         <v>1010</v>
@@ -2263,13 +2263,13 @@
         <v>2025</v>
       </c>
       <c r="C80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F80">
         <v>180</v>
@@ -2283,13 +2283,13 @@
         <v>2025</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F81">
         <v>331</v>
@@ -2323,13 +2323,13 @@
         <v>2026</v>
       </c>
       <c r="C83" t="s">
+        <v>76</v>
+      </c>
+      <c r="D83" t="s">
         <v>38</v>
       </c>
-      <c r="D83" t="s">
-        <v>39</v>
-      </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F83">
         <v>1560</v>
@@ -2349,7 +2349,7 @@
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F84">
         <v>2003</v>
@@ -2363,13 +2363,13 @@
         <v>2026</v>
       </c>
       <c r="C85" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F85">
         <v>443</v>
@@ -2403,13 +2403,13 @@
         <v>2026</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F87">
         <v>465</v>
@@ -2423,13 +2423,13 @@
         <v>2026</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F88">
         <v>433</v>
@@ -2443,13 +2443,13 @@
         <v>2026</v>
       </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F89">
         <v>50</v>
@@ -2483,13 +2483,13 @@
         <v>2026</v>
       </c>
       <c r="C91" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F91">
         <v>391</v>
@@ -2503,13 +2503,13 @@
         <v>2026</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F92">
         <v>1558</v>
@@ -2529,7 +2529,7 @@
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F93">
         <v>1069</v>
@@ -2543,13 +2543,13 @@
         <v>2026</v>
       </c>
       <c r="C94" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94" t="s">
+        <v>42</v>
+      </c>
+      <c r="E94" t="s">
         <v>48</v>
-      </c>
-      <c r="D94" t="s">
-        <v>43</v>
-      </c>
-      <c r="E94" t="s">
-        <v>49</v>
       </c>
       <c r="F94">
         <v>3321</v>
@@ -2563,13 +2563,13 @@
         <v>2026</v>
       </c>
       <c r="C95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F95">
         <v>820</v>
@@ -2583,13 +2583,13 @@
         <v>2026</v>
       </c>
       <c r="C96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F96">
         <v>1266</v>
@@ -2623,13 +2623,13 @@
         <v>2026</v>
       </c>
       <c r="C98" t="s">
+        <v>51</v>
+      </c>
+      <c r="D98" t="s">
+        <v>42</v>
+      </c>
+      <c r="E98" t="s">
         <v>52</v>
-      </c>
-      <c r="D98" t="s">
-        <v>43</v>
-      </c>
-      <c r="E98" t="s">
-        <v>53</v>
       </c>
       <c r="F98">
         <v>1059</v>
@@ -2649,7 +2649,7 @@
         <v>35</v>
       </c>
       <c r="E99" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F99">
         <v>3732</v>
@@ -2663,13 +2663,13 @@
         <v>2026</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F100">
         <v>3577</v>
@@ -2683,13 +2683,13 @@
         <v>2026</v>
       </c>
       <c r="C101" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D101" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F101">
         <v>315</v>
@@ -2746,10 +2746,10 @@
         <v>30</v>
       </c>
       <c r="D104" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F104">
         <v>1626</v>
@@ -2763,13 +2763,13 @@
         <v>2026</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F105">
         <v>1941</v>
@@ -2789,7 +2789,7 @@
         <v>35</v>
       </c>
       <c r="E106" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F106">
         <v>4341</v>
@@ -2803,13 +2803,13 @@
         <v>2026</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E107" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F107">
         <v>1611</v>
@@ -2863,13 +2863,13 @@
         <v>2026</v>
       </c>
       <c r="C110" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F110">
         <v>449</v>
@@ -2883,13 +2883,13 @@
         <v>2026</v>
       </c>
       <c r="C111" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D111" t="s">
         <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F111">
         <v>1254</v>
@@ -2903,13 +2903,13 @@
         <v>2026</v>
       </c>
       <c r="C112" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D112" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F112">
         <v>405</v>
@@ -2923,13 +2923,13 @@
         <v>2026</v>
       </c>
       <c r="C113" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D113" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F113">
         <v>1459</v>
@@ -2943,13 +2943,13 @@
         <v>2026</v>
       </c>
       <c r="C114" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F114">
         <v>1055</v>
@@ -2963,13 +2963,13 @@
         <v>2026</v>
       </c>
       <c r="C115" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F115">
         <v>501</v>
@@ -2983,13 +2983,13 @@
         <v>2026</v>
       </c>
       <c r="C116" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D116" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F116">
         <v>300</v>
@@ -3003,13 +3003,13 @@
         <v>2026</v>
       </c>
       <c r="C117" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D117" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F117">
         <v>60</v>
@@ -3043,13 +3043,13 @@
         <v>2025</v>
       </c>
       <c r="C119" t="s">
+        <v>76</v>
+      </c>
+      <c r="D119" t="s">
         <v>38</v>
       </c>
-      <c r="D119" t="s">
-        <v>39</v>
-      </c>
       <c r="E119" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F119">
         <v>1560</v>
@@ -3069,7 +3069,7 @@
         <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F120">
         <v>1321</v>
@@ -3103,13 +3103,13 @@
         <v>2025</v>
       </c>
       <c r="C122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D122" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F122">
         <v>286</v>
@@ -3123,13 +3123,13 @@
         <v>2025</v>
       </c>
       <c r="C123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D123" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F123">
         <v>274</v>
@@ -3143,13 +3143,13 @@
         <v>2025</v>
       </c>
       <c r="C124" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D124" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F124">
         <v>40</v>
@@ -3183,13 +3183,13 @@
         <v>2025</v>
       </c>
       <c r="C126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D126" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F126">
         <v>378</v>
@@ -3203,13 +3203,13 @@
         <v>2025</v>
       </c>
       <c r="C127" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D127" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F127">
         <v>1744</v>
@@ -3229,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="E128" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F128">
         <v>1304</v>
@@ -3243,13 +3243,13 @@
         <v>2025</v>
       </c>
       <c r="C129" t="s">
+        <v>47</v>
+      </c>
+      <c r="D129" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" t="s">
         <v>48</v>
-      </c>
-      <c r="D129" t="s">
-        <v>43</v>
-      </c>
-      <c r="E129" t="s">
-        <v>49</v>
       </c>
       <c r="F129">
         <v>1785</v>
@@ -3263,13 +3263,13 @@
         <v>2025</v>
       </c>
       <c r="C130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F130">
         <v>691</v>
@@ -3283,13 +3283,13 @@
         <v>2025</v>
       </c>
       <c r="C131" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D131" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F131">
         <v>1339</v>
@@ -3323,13 +3323,13 @@
         <v>2025</v>
       </c>
       <c r="C133" t="s">
+        <v>51</v>
+      </c>
+      <c r="D133" t="s">
+        <v>42</v>
+      </c>
+      <c r="E133" t="s">
         <v>52</v>
-      </c>
-      <c r="D133" t="s">
-        <v>43</v>
-      </c>
-      <c r="E133" t="s">
-        <v>53</v>
       </c>
       <c r="F133">
         <v>434</v>
@@ -3349,7 +3349,7 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F134">
         <v>2775</v>
@@ -3363,13 +3363,13 @@
         <v>2025</v>
       </c>
       <c r="C135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F135">
         <v>3469</v>
@@ -3383,13 +3383,13 @@
         <v>2025</v>
       </c>
       <c r="C136" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D136" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F136">
         <v>225</v>
@@ -3463,13 +3463,13 @@
         <v>2025</v>
       </c>
       <c r="C140" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F140">
         <v>1650</v>
@@ -3489,7 +3489,7 @@
         <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F141">
         <v>4127</v>
@@ -3503,13 +3503,13 @@
         <v>2025</v>
       </c>
       <c r="C142" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D142" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F142">
         <v>3291</v>
@@ -3563,13 +3563,13 @@
         <v>2025</v>
       </c>
       <c r="C145" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D145" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F145">
         <v>143</v>
@@ -3583,13 +3583,13 @@
         <v>2025</v>
       </c>
       <c r="C146" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D146" t="s">
         <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F146">
         <v>1375</v>
@@ -3603,13 +3603,13 @@
         <v>2025</v>
       </c>
       <c r="C147" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D147" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E147" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F147">
         <v>1192</v>
@@ -3623,13 +3623,13 @@
         <v>2025</v>
       </c>
       <c r="C148" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D148" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E148" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F148">
         <v>699</v>
@@ -3643,13 +3643,13 @@
         <v>2025</v>
       </c>
       <c r="C149" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F149">
         <v>233</v>
@@ -3663,13 +3663,13 @@
         <v>2025</v>
       </c>
       <c r="C150" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F150">
         <v>226</v>
@@ -3683,13 +3683,13 @@
         <v>2025</v>
       </c>
       <c r="C151" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D151" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F151">
         <v>301</v>
@@ -3723,13 +3723,13 @@
         <v>2025</v>
       </c>
       <c r="C153" t="s">
+        <v>76</v>
+      </c>
+      <c r="D153" t="s">
         <v>38</v>
       </c>
-      <c r="D153" t="s">
-        <v>39</v>
-      </c>
       <c r="E153" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F153">
         <v>1820</v>
@@ -3749,7 +3749,7 @@
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F154">
         <v>1522</v>
@@ -3763,13 +3763,13 @@
         <v>2025</v>
       </c>
       <c r="C155" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D155" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F155">
         <v>230</v>
@@ -3783,13 +3783,13 @@
         <v>2025</v>
       </c>
       <c r="C156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F156">
         <v>496</v>
@@ -3823,13 +3823,13 @@
         <v>2025</v>
       </c>
       <c r="C158" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D158" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E158" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F158">
         <v>135</v>
@@ -3843,13 +3843,13 @@
         <v>2025</v>
       </c>
       <c r="C159" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F159">
         <v>2011</v>
@@ -3869,7 +3869,7 @@
         <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F160">
         <v>1279</v>
@@ -3883,13 +3883,13 @@
         <v>2025</v>
       </c>
       <c r="C161" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" t="s">
+        <v>42</v>
+      </c>
+      <c r="E161" t="s">
         <v>48</v>
-      </c>
-      <c r="D161" t="s">
-        <v>43</v>
-      </c>
-      <c r="E161" t="s">
-        <v>49</v>
       </c>
       <c r="F161">
         <v>1509</v>
@@ -3903,13 +3903,13 @@
         <v>2025</v>
       </c>
       <c r="C162" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D162" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F162">
         <v>2046</v>
@@ -3943,13 +3943,13 @@
         <v>2025</v>
       </c>
       <c r="C164" t="s">
+        <v>51</v>
+      </c>
+      <c r="D164" t="s">
+        <v>42</v>
+      </c>
+      <c r="E164" t="s">
         <v>52</v>
-      </c>
-      <c r="D164" t="s">
-        <v>43</v>
-      </c>
-      <c r="E164" t="s">
-        <v>53</v>
       </c>
       <c r="F164">
         <v>162</v>
@@ -3969,7 +3969,7 @@
         <v>35</v>
       </c>
       <c r="E165" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F165">
         <v>2931</v>
@@ -3983,13 +3983,13 @@
         <v>2025</v>
       </c>
       <c r="C166" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E166" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F166">
         <v>3333</v>
@@ -4003,13 +4003,13 @@
         <v>2025</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D167" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E167" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F167">
         <v>414</v>
@@ -4023,13 +4023,13 @@
         <v>2025</v>
       </c>
       <c r="C168" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D168" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F168">
         <v>390</v>
@@ -4086,10 +4086,10 @@
         <v>30</v>
       </c>
       <c r="D171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F171">
         <v>833</v>
@@ -4103,13 +4103,13 @@
         <v>2025</v>
       </c>
       <c r="C172" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D172" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E172" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F172">
         <v>2288</v>
@@ -4129,7 +4129,7 @@
         <v>35</v>
       </c>
       <c r="E173" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F173">
         <v>4069</v>
@@ -4143,13 +4143,13 @@
         <v>2025</v>
       </c>
       <c r="C174" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D174" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E174" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F174">
         <v>1500</v>
@@ -4183,13 +4183,13 @@
         <v>2025</v>
       </c>
       <c r="C176" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D176" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E176" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F176">
         <v>180</v>
@@ -4203,13 +4203,13 @@
         <v>2025</v>
       </c>
       <c r="C177" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D177" t="s">
         <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F177">
         <v>1254</v>
@@ -4243,13 +4243,13 @@
         <v>2025</v>
       </c>
       <c r="C179" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D179" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E179" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F179">
         <v>1544</v>
@@ -4263,13 +4263,13 @@
         <v>2025</v>
       </c>
       <c r="C180" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D180" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E180" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F180">
         <v>1077</v>
@@ -4283,13 +4283,13 @@
         <v>2025</v>
       </c>
       <c r="C181" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D181" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E181" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F181">
         <v>180</v>
@@ -4303,13 +4303,13 @@
         <v>2025</v>
       </c>
       <c r="C182" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D182" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F182">
         <v>312</v>
@@ -4343,13 +4343,13 @@
         <v>2026</v>
       </c>
       <c r="C184" t="s">
+        <v>76</v>
+      </c>
+      <c r="D184" t="s">
         <v>38</v>
       </c>
-      <c r="D184" t="s">
-        <v>39</v>
-      </c>
       <c r="E184" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F184">
         <v>1560</v>
@@ -4369,7 +4369,7 @@
         <v>8</v>
       </c>
       <c r="E185" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F185">
         <v>1380</v>
@@ -4383,13 +4383,13 @@
         <v>2026</v>
       </c>
       <c r="C186" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D186" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E186" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F186">
         <v>280</v>
@@ -4423,13 +4423,13 @@
         <v>2026</v>
       </c>
       <c r="C188" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D188" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E188" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F188">
         <v>325</v>
@@ -4443,13 +4443,13 @@
         <v>2026</v>
       </c>
       <c r="C189" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D189" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E189" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F189">
         <v>445</v>
@@ -4463,13 +4463,13 @@
         <v>2026</v>
       </c>
       <c r="C190" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D190" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -4503,13 +4503,13 @@
         <v>2026</v>
       </c>
       <c r="C192" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E192" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F192">
         <v>203</v>
@@ -4523,13 +4523,13 @@
         <v>2026</v>
       </c>
       <c r="C193" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D193" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E193" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F193">
         <v>1698</v>
@@ -4549,7 +4549,7 @@
         <v>8</v>
       </c>
       <c r="E194" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F194">
         <v>939</v>
@@ -4563,13 +4563,13 @@
         <v>2026</v>
       </c>
       <c r="C195" t="s">
+        <v>47</v>
+      </c>
+      <c r="D195" t="s">
+        <v>42</v>
+      </c>
+      <c r="E195" t="s">
         <v>48</v>
-      </c>
-      <c r="D195" t="s">
-        <v>43</v>
-      </c>
-      <c r="E195" t="s">
-        <v>49</v>
       </c>
       <c r="F195">
         <v>1960</v>
@@ -4583,13 +4583,13 @@
         <v>2026</v>
       </c>
       <c r="C196" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D196" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E196" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F196">
         <v>1388</v>
@@ -4603,13 +4603,13 @@
         <v>2026</v>
       </c>
       <c r="C197" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E197" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F197">
         <v>1360</v>
@@ -4643,13 +4643,13 @@
         <v>2026</v>
       </c>
       <c r="C199" t="s">
+        <v>51</v>
+      </c>
+      <c r="D199" t="s">
+        <v>42</v>
+      </c>
+      <c r="E199" t="s">
         <v>52</v>
-      </c>
-      <c r="D199" t="s">
-        <v>43</v>
-      </c>
-      <c r="E199" t="s">
-        <v>53</v>
       </c>
       <c r="F199">
         <v>741</v>
@@ -4669,7 +4669,7 @@
         <v>35</v>
       </c>
       <c r="E200" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F200">
         <v>3643</v>
@@ -4683,13 +4683,13 @@
         <v>2026</v>
       </c>
       <c r="C201" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E201" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F201">
         <v>3535</v>
@@ -4703,13 +4703,13 @@
         <v>2026</v>
       </c>
       <c r="C202" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D202" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E202" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F202">
         <v>470</v>
@@ -4766,10 +4766,10 @@
         <v>30</v>
       </c>
       <c r="D205" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E205" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F205">
         <v>1853</v>
@@ -4783,13 +4783,13 @@
         <v>2026</v>
       </c>
       <c r="C206" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D206" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E206" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F206">
         <v>1815</v>
@@ -4809,7 +4809,7 @@
         <v>35</v>
       </c>
       <c r="E207" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F207">
         <v>4338</v>
@@ -4823,13 +4823,13 @@
         <v>2026</v>
       </c>
       <c r="C208" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D208" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E208" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F208">
         <v>1500</v>
@@ -4883,13 +4883,13 @@
         <v>2026</v>
       </c>
       <c r="C211" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D211" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E211" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F211">
         <v>120</v>
@@ -4903,13 +4903,13 @@
         <v>2026</v>
       </c>
       <c r="C212" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D212" t="s">
         <v>8</v>
       </c>
       <c r="E212" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F212">
         <v>1254</v>
@@ -4923,13 +4923,13 @@
         <v>2026</v>
       </c>
       <c r="C213" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D213" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F213">
         <v>335</v>
@@ -4943,13 +4943,13 @@
         <v>2026</v>
       </c>
       <c r="C214" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D214" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E214" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F214">
         <v>1241</v>
@@ -4963,13 +4963,13 @@
         <v>2026</v>
       </c>
       <c r="C215" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E215" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F215">
         <v>1260</v>
@@ -4983,13 +4983,13 @@
         <v>2026</v>
       </c>
       <c r="C216" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D216" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E216" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F216">
         <v>165</v>
@@ -5003,13 +5003,13 @@
         <v>2026</v>
       </c>
       <c r="C217" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D217" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E217" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F217">
         <v>315</v>
@@ -5023,13 +5023,13 @@
         <v>2026</v>
       </c>
       <c r="C218" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D218" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E218" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F218">
         <v>150</v>
@@ -5063,13 +5063,13 @@
         <v>2025</v>
       </c>
       <c r="C220" t="s">
+        <v>76</v>
+      </c>
+      <c r="D220" t="s">
         <v>38</v>
       </c>
-      <c r="D220" t="s">
-        <v>39</v>
-      </c>
       <c r="E220" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F220">
         <v>1820</v>
@@ -5089,7 +5089,7 @@
         <v>8</v>
       </c>
       <c r="E221" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F221">
         <v>1408</v>
@@ -5103,13 +5103,13 @@
         <v>2025</v>
       </c>
       <c r="C222" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D222" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E222" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F222">
         <v>157</v>
@@ -5123,13 +5123,13 @@
         <v>2025</v>
       </c>
       <c r="C223" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D223" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E223" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F223">
         <v>317</v>
@@ -5163,13 +5163,13 @@
         <v>2025</v>
       </c>
       <c r="C225" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D225" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E225" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F225">
         <v>45</v>
@@ -5183,13 +5183,13 @@
         <v>2025</v>
       </c>
       <c r="C226" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D226" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E226" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F226">
         <v>1396</v>
@@ -5209,7 +5209,7 @@
         <v>8</v>
       </c>
       <c r="E227" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F227">
         <v>1334</v>
@@ -5223,13 +5223,13 @@
         <v>2025</v>
       </c>
       <c r="C228" t="s">
+        <v>47</v>
+      </c>
+      <c r="D228" t="s">
+        <v>42</v>
+      </c>
+      <c r="E228" t="s">
         <v>48</v>
-      </c>
-      <c r="D228" t="s">
-        <v>43</v>
-      </c>
-      <c r="E228" t="s">
-        <v>49</v>
       </c>
       <c r="F228">
         <v>1365</v>
@@ -5243,13 +5243,13 @@
         <v>2025</v>
       </c>
       <c r="C229" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E229" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F229">
         <v>1734</v>
@@ -5283,13 +5283,13 @@
         <v>2025</v>
       </c>
       <c r="C231" t="s">
+        <v>51</v>
+      </c>
+      <c r="D231" t="s">
+        <v>42</v>
+      </c>
+      <c r="E231" t="s">
         <v>52</v>
-      </c>
-      <c r="D231" t="s">
-        <v>43</v>
-      </c>
-      <c r="E231" t="s">
-        <v>53</v>
       </c>
       <c r="F231">
         <v>381</v>
@@ -5309,7 +5309,7 @@
         <v>35</v>
       </c>
       <c r="E232" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F232">
         <v>3194</v>
@@ -5323,13 +5323,13 @@
         <v>2025</v>
       </c>
       <c r="C233" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D233" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E233" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F233">
         <v>3333</v>
@@ -5343,13 +5343,13 @@
         <v>2025</v>
       </c>
       <c r="C234" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D234" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E234" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F234">
         <v>234</v>
@@ -5363,13 +5363,13 @@
         <v>2025</v>
       </c>
       <c r="C235" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D235" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E235" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F235">
         <v>571</v>
@@ -5426,10 +5426,10 @@
         <v>30</v>
       </c>
       <c r="D238" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E238" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F238">
         <v>195</v>
@@ -5443,13 +5443,13 @@
         <v>2025</v>
       </c>
       <c r="C239" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D239" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E239" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F239">
         <v>2063</v>
@@ -5469,7 +5469,7 @@
         <v>35</v>
       </c>
       <c r="E240" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F240">
         <v>4099</v>
@@ -5483,13 +5483,13 @@
         <v>2025</v>
       </c>
       <c r="C241" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D241" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E241" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F241">
         <v>1500</v>
@@ -5523,13 +5523,13 @@
         <v>2025</v>
       </c>
       <c r="C243" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D243" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E243" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F243">
         <v>369</v>
@@ -5543,13 +5543,13 @@
         <v>2025</v>
       </c>
       <c r="C244" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D244" t="s">
         <v>8</v>
       </c>
       <c r="E244" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F244">
         <v>1254</v>
@@ -5583,13 +5583,13 @@
         <v>2025</v>
       </c>
       <c r="C246" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D246" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F246">
         <v>1344</v>
@@ -5603,13 +5603,13 @@
         <v>2025</v>
       </c>
       <c r="C247" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D247" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E247" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F247">
         <v>643</v>
@@ -5623,13 +5623,13 @@
         <v>2025</v>
       </c>
       <c r="C248" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D248" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E248" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F248">
         <v>316</v>
@@ -5643,13 +5643,13 @@
         <v>2025</v>
       </c>
       <c r="C249" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D249" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E249" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F249">
         <v>161</v>
@@ -5683,13 +5683,13 @@
         <v>2026</v>
       </c>
       <c r="C251" t="s">
+        <v>76</v>
+      </c>
+      <c r="D251" t="s">
         <v>38</v>
       </c>
-      <c r="D251" t="s">
-        <v>39</v>
-      </c>
       <c r="E251" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F251">
         <v>1560</v>
@@ -5709,7 +5709,7 @@
         <v>8</v>
       </c>
       <c r="E252" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F252">
         <v>2092</v>
@@ -5723,13 +5723,13 @@
         <v>2026</v>
       </c>
       <c r="C253" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D253" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E253" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -5763,13 +5763,13 @@
         <v>2026</v>
       </c>
       <c r="C255" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D255" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E255" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F255">
         <v>488</v>
@@ -5783,13 +5783,13 @@
         <v>2026</v>
       </c>
       <c r="C256" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D256" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E256" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F256">
         <v>103</v>
@@ -5803,13 +5803,13 @@
         <v>2026</v>
       </c>
       <c r="C257" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D257" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E257" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F257">
         <v>340</v>
@@ -5843,13 +5843,13 @@
         <v>2026</v>
       </c>
       <c r="C259" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D259" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E259" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F259">
         <v>960</v>
@@ -5863,13 +5863,13 @@
         <v>2026</v>
       </c>
       <c r="C260" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D260" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E260" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F260">
         <v>1533</v>
@@ -5889,7 +5889,7 @@
         <v>8</v>
       </c>
       <c r="E261" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F261">
         <v>1149</v>
@@ -5903,13 +5903,13 @@
         <v>2026</v>
       </c>
       <c r="C262" t="s">
+        <v>47</v>
+      </c>
+      <c r="D262" t="s">
+        <v>42</v>
+      </c>
+      <c r="E262" t="s">
         <v>48</v>
-      </c>
-      <c r="D262" t="s">
-        <v>43</v>
-      </c>
-      <c r="E262" t="s">
-        <v>49</v>
       </c>
       <c r="F262">
         <v>2468</v>
@@ -5923,13 +5923,13 @@
         <v>2026</v>
       </c>
       <c r="C263" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D263" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E263" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F263">
         <v>1088</v>
@@ -5943,13 +5943,13 @@
         <v>2026</v>
       </c>
       <c r="C264" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E264" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F264">
         <v>1948</v>
@@ -5983,13 +5983,13 @@
         <v>2026</v>
       </c>
       <c r="C266" t="s">
+        <v>51</v>
+      </c>
+      <c r="D266" t="s">
+        <v>42</v>
+      </c>
+      <c r="E266" t="s">
         <v>52</v>
-      </c>
-      <c r="D266" t="s">
-        <v>43</v>
-      </c>
-      <c r="E266" t="s">
-        <v>53</v>
       </c>
       <c r="F266">
         <v>558</v>
@@ -6009,7 +6009,7 @@
         <v>35</v>
       </c>
       <c r="E267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F267">
         <v>4120</v>
@@ -6023,13 +6023,13 @@
         <v>2026</v>
       </c>
       <c r="C268" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D268" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E268" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F268">
         <v>3627</v>
@@ -6043,13 +6043,13 @@
         <v>2026</v>
       </c>
       <c r="C269" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D269" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E269" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F269">
         <v>783</v>
@@ -6106,10 +6106,10 @@
         <v>30</v>
       </c>
       <c r="D272" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E272" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F272">
         <v>1805</v>
@@ -6123,13 +6123,13 @@
         <v>2026</v>
       </c>
       <c r="C273" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D273" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E273" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F273">
         <v>2140</v>
@@ -6149,7 +6149,7 @@
         <v>35</v>
       </c>
       <c r="E274" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F274">
         <v>4951</v>
@@ -6163,13 +6163,13 @@
         <v>2026</v>
       </c>
       <c r="C275" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D275" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E275" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F275">
         <v>1650</v>
@@ -6223,13 +6223,13 @@
         <v>2026</v>
       </c>
       <c r="C278" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D278" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E278" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F278">
         <v>530</v>
@@ -6243,13 +6243,13 @@
         <v>2026</v>
       </c>
       <c r="C279" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D279" t="s">
         <v>8</v>
       </c>
       <c r="E279" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F279">
         <v>1254</v>
@@ -6263,13 +6263,13 @@
         <v>2026</v>
       </c>
       <c r="C280" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D280" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E280" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F280">
         <v>270</v>
@@ -6283,13 +6283,13 @@
         <v>2026</v>
       </c>
       <c r="C281" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D281" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E281" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F281">
         <v>2019</v>
@@ -6303,13 +6303,13 @@
         <v>2026</v>
       </c>
       <c r="C282" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D282" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E282" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F282">
         <v>1130</v>
@@ -6323,13 +6323,13 @@
         <v>2026</v>
       </c>
       <c r="C283" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D283" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E283" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F283">
         <v>458</v>
@@ -6343,13 +6343,13 @@
         <v>2026</v>
       </c>
       <c r="C284" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D284" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E284" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F284">
         <v>143</v>
@@ -6363,13 +6363,13 @@
         <v>2026</v>
       </c>
       <c r="C285" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D285" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E285" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F285">
         <v>668</v>
@@ -6403,13 +6403,13 @@
         <v>2025</v>
       </c>
       <c r="C287" t="s">
+        <v>76</v>
+      </c>
+      <c r="D287" t="s">
         <v>38</v>
       </c>
-      <c r="D287" t="s">
-        <v>39</v>
-      </c>
       <c r="E287" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F287">
         <v>1820</v>
@@ -6429,7 +6429,7 @@
         <v>8</v>
       </c>
       <c r="E288" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F288">
         <v>1743</v>
@@ -6463,13 +6463,13 @@
         <v>2025</v>
       </c>
       <c r="C290" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D290" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E290" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F290">
         <v>68</v>
@@ -6483,13 +6483,13 @@
         <v>2025</v>
       </c>
       <c r="C291" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D291" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E291" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F291">
         <v>216</v>
@@ -6523,13 +6523,13 @@
         <v>2025</v>
       </c>
       <c r="C293" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D293" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E293" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F293">
         <v>45</v>
@@ -6543,13 +6543,13 @@
         <v>2025</v>
       </c>
       <c r="C294" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D294" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E294" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F294">
         <v>1001</v>
@@ -6569,7 +6569,7 @@
         <v>8</v>
       </c>
       <c r="E295" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F295">
         <v>1672</v>
@@ -6583,13 +6583,13 @@
         <v>2025</v>
       </c>
       <c r="C296" t="s">
+        <v>47</v>
+      </c>
+      <c r="D296" t="s">
+        <v>42</v>
+      </c>
+      <c r="E296" t="s">
         <v>48</v>
-      </c>
-      <c r="D296" t="s">
-        <v>43</v>
-      </c>
-      <c r="E296" t="s">
-        <v>49</v>
       </c>
       <c r="F296">
         <v>1343</v>
@@ -6603,13 +6603,13 @@
         <v>2025</v>
       </c>
       <c r="C297" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D297" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E297" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F297">
         <v>292</v>
@@ -6623,13 +6623,13 @@
         <v>2025</v>
       </c>
       <c r="C298" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D298" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E298" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F298">
         <v>1215</v>
@@ -6663,13 +6663,13 @@
         <v>2025</v>
       </c>
       <c r="C300" t="s">
+        <v>51</v>
+      </c>
+      <c r="D300" t="s">
+        <v>42</v>
+      </c>
+      <c r="E300" t="s">
         <v>52</v>
-      </c>
-      <c r="D300" t="s">
-        <v>43</v>
-      </c>
-      <c r="E300" t="s">
-        <v>53</v>
       </c>
       <c r="F300">
         <v>636</v>
@@ -6689,7 +6689,7 @@
         <v>35</v>
       </c>
       <c r="E301" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F301">
         <v>3145</v>
@@ -6703,13 +6703,13 @@
         <v>2025</v>
       </c>
       <c r="C302" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D302" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E302" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F302">
         <v>3333</v>
@@ -6743,13 +6743,13 @@
         <v>2025</v>
       </c>
       <c r="C304" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D304" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E304" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F304">
         <v>149</v>
@@ -6763,13 +6763,13 @@
         <v>2025</v>
       </c>
       <c r="C305" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D305" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E305" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F305">
         <v>280</v>
@@ -6826,10 +6826,10 @@
         <v>30</v>
       </c>
       <c r="D308" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E308" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F308">
         <v>591</v>
@@ -6843,13 +6843,13 @@
         <v>2025</v>
       </c>
       <c r="C309" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D309" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E309" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F309">
         <v>1699</v>
@@ -6869,7 +6869,7 @@
         <v>35</v>
       </c>
       <c r="E310" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F310">
         <v>3828</v>
@@ -6883,13 +6883,13 @@
         <v>2025</v>
       </c>
       <c r="C311" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D311" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E311" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F311">
         <v>1645</v>
@@ -6923,13 +6923,13 @@
         <v>2025</v>
       </c>
       <c r="C313" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D313" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E313" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F313">
         <v>160</v>
@@ -6943,13 +6943,13 @@
         <v>2025</v>
       </c>
       <c r="C314" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D314" t="s">
         <v>8</v>
       </c>
       <c r="E314" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F314">
         <v>1375</v>
@@ -6963,13 +6963,13 @@
         <v>2025</v>
       </c>
       <c r="C315" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D315" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E315" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F315">
         <v>662</v>
@@ -6983,13 +6983,13 @@
         <v>2025</v>
       </c>
       <c r="C316" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D316" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E316" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F316">
         <v>1445</v>
@@ -7003,13 +7003,13 @@
         <v>2025</v>
       </c>
       <c r="C317" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D317" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E317" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F317">
         <v>646</v>
@@ -7023,13 +7023,13 @@
         <v>2025</v>
       </c>
       <c r="C318" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D318" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E318" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F318">
         <v>129</v>
@@ -7043,13 +7043,13 @@
         <v>2025</v>
       </c>
       <c r="C319" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D319" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E319" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F319">
         <v>126</v>
@@ -7083,13 +7083,13 @@
         <v>2026</v>
       </c>
       <c r="C321" t="s">
+        <v>76</v>
+      </c>
+      <c r="D321" t="s">
         <v>38</v>
       </c>
-      <c r="D321" t="s">
-        <v>39</v>
-      </c>
       <c r="E321" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F321">
         <v>1560</v>
@@ -7103,7 +7103,7 @@
         <v>2026</v>
       </c>
       <c r="C322" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D322" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="E323" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F323">
         <v>1877</v>
@@ -7143,13 +7143,13 @@
         <v>2026</v>
       </c>
       <c r="C324" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D324" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E324" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F324">
         <v>533</v>
@@ -7183,13 +7183,13 @@
         <v>2026</v>
       </c>
       <c r="C326" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D326" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E326" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F326">
         <v>235</v>
@@ -7203,13 +7203,13 @@
         <v>2026</v>
       </c>
       <c r="C327" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D327" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E327" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F327">
         <v>183</v>
@@ -7223,13 +7223,13 @@
         <v>2026</v>
       </c>
       <c r="C328" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D328" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E328" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F328">
         <v>30</v>
@@ -7263,13 +7263,13 @@
         <v>2026</v>
       </c>
       <c r="C330" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D330" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E330" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F330">
         <v>253</v>
@@ -7283,13 +7283,13 @@
         <v>2026</v>
       </c>
       <c r="C331" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D331" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E331" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F331">
         <v>1176</v>
@@ -7309,7 +7309,7 @@
         <v>8</v>
       </c>
       <c r="E332" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F332">
         <v>1496</v>
@@ -7323,13 +7323,13 @@
         <v>2026</v>
       </c>
       <c r="C333" t="s">
+        <v>47</v>
+      </c>
+      <c r="D333" t="s">
+        <v>42</v>
+      </c>
+      <c r="E333" t="s">
         <v>48</v>
-      </c>
-      <c r="D333" t="s">
-        <v>43</v>
-      </c>
-      <c r="E333" t="s">
-        <v>49</v>
       </c>
       <c r="F333">
         <v>1737</v>
@@ -7343,13 +7343,13 @@
         <v>2026</v>
       </c>
       <c r="C334" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D334" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E334" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F334">
         <v>480</v>
@@ -7363,13 +7363,13 @@
         <v>2026</v>
       </c>
       <c r="C335" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D335" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E335" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F335">
         <v>790</v>
@@ -7403,13 +7403,13 @@
         <v>2026</v>
       </c>
       <c r="C337" t="s">
+        <v>51</v>
+      </c>
+      <c r="D337" t="s">
+        <v>42</v>
+      </c>
+      <c r="E337" t="s">
         <v>52</v>
-      </c>
-      <c r="D337" t="s">
-        <v>43</v>
-      </c>
-      <c r="E337" t="s">
-        <v>53</v>
       </c>
       <c r="F337">
         <v>1418</v>
@@ -7429,7 +7429,7 @@
         <v>35</v>
       </c>
       <c r="E338" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F338">
         <v>3496</v>
@@ -7443,13 +7443,13 @@
         <v>2026</v>
       </c>
       <c r="C339" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D339" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E339" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F339">
         <v>3640</v>
@@ -7463,13 +7463,13 @@
         <v>2026</v>
       </c>
       <c r="C340" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D340" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E340" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F340">
         <v>300</v>
@@ -7526,10 +7526,10 @@
         <v>30</v>
       </c>
       <c r="D343" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E343" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F343">
         <v>710</v>
@@ -7543,13 +7543,13 @@
         <v>2026</v>
       </c>
       <c r="C344" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D344" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E344" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F344">
         <v>1185</v>
@@ -7569,7 +7569,7 @@
         <v>35</v>
       </c>
       <c r="E345" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F345">
         <v>3942</v>
@@ -7583,13 +7583,13 @@
         <v>2026</v>
       </c>
       <c r="C346" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D346" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E346" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F346">
         <v>1645</v>
@@ -7603,13 +7603,13 @@
         <v>2026</v>
       </c>
       <c r="C347" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D347" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E347" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F347">
         <v>130</v>
@@ -7623,13 +7623,13 @@
         <v>2026</v>
       </c>
       <c r="C348" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D348" t="s">
         <v>8</v>
       </c>
       <c r="E348" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F348">
         <v>1375</v>
@@ -7643,13 +7643,13 @@
         <v>2026</v>
       </c>
       <c r="C349" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D349" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E349" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F349">
         <v>75</v>
@@ -7663,13 +7663,13 @@
         <v>2026</v>
       </c>
       <c r="C350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D350" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E350" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F350">
         <v>1172</v>
@@ -7683,13 +7683,13 @@
         <v>2026</v>
       </c>
       <c r="C351" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D351" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E351" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F351">
         <v>864</v>
@@ -7703,13 +7703,13 @@
         <v>2026</v>
       </c>
       <c r="C352" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D352" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E352" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F352">
         <v>360</v>
@@ -7723,13 +7723,13 @@
         <v>2026</v>
       </c>
       <c r="C353" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D353" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E353" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F353">
         <v>60</v>
@@ -7743,13 +7743,13 @@
         <v>2026</v>
       </c>
       <c r="C354" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D354" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E354" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F354">
         <v>282</v>
@@ -7783,13 +7783,13 @@
         <v>2025</v>
       </c>
       <c r="C356" t="s">
+        <v>76</v>
+      </c>
+      <c r="D356" t="s">
         <v>38</v>
       </c>
-      <c r="D356" t="s">
-        <v>39</v>
-      </c>
       <c r="E356" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F356">
         <v>1560</v>
@@ -7809,7 +7809,7 @@
         <v>8</v>
       </c>
       <c r="E357" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F357">
         <v>1353</v>
@@ -7843,13 +7843,13 @@
         <v>2025</v>
       </c>
       <c r="C359" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D359" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E359" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F359">
         <v>485</v>
@@ -7883,13 +7883,13 @@
         <v>2025</v>
       </c>
       <c r="C361" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D361" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E361" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F361">
         <v>469</v>
@@ -7909,7 +7909,7 @@
         <v>8</v>
       </c>
       <c r="E362" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F362">
         <v>1008</v>
@@ -7923,13 +7923,13 @@
         <v>2025</v>
       </c>
       <c r="C363" t="s">
+        <v>47</v>
+      </c>
+      <c r="D363" t="s">
+        <v>42</v>
+      </c>
+      <c r="E363" t="s">
         <v>48</v>
-      </c>
-      <c r="D363" t="s">
-        <v>43</v>
-      </c>
-      <c r="E363" t="s">
-        <v>49</v>
       </c>
       <c r="F363">
         <v>1588</v>
@@ -7943,13 +7943,13 @@
         <v>2025</v>
       </c>
       <c r="C364" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D364" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E364" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F364">
         <v>103</v>
@@ -7963,13 +7963,13 @@
         <v>2025</v>
       </c>
       <c r="C365" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D365" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E365" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F365">
         <v>799</v>
@@ -8003,13 +8003,13 @@
         <v>2025</v>
       </c>
       <c r="C367" t="s">
+        <v>51</v>
+      </c>
+      <c r="D367" t="s">
+        <v>42</v>
+      </c>
+      <c r="E367" t="s">
         <v>52</v>
-      </c>
-      <c r="D367" t="s">
-        <v>43</v>
-      </c>
-      <c r="E367" t="s">
-        <v>53</v>
       </c>
       <c r="F367">
         <v>254</v>
@@ -8029,7 +8029,7 @@
         <v>35</v>
       </c>
       <c r="E368" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F368">
         <v>2597</v>
@@ -8043,13 +8043,13 @@
         <v>2025</v>
       </c>
       <c r="C369" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D369" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E369" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F369">
         <v>3333</v>
@@ -8123,13 +8123,13 @@
         <v>2025</v>
       </c>
       <c r="C373" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D373" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E373" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F373">
         <v>576</v>
@@ -8149,7 +8149,7 @@
         <v>35</v>
       </c>
       <c r="E374" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F374">
         <v>4668</v>
@@ -8163,13 +8163,13 @@
         <v>2025</v>
       </c>
       <c r="C375" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D375" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E375" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F375">
         <v>2194</v>
@@ -8223,13 +8223,13 @@
         <v>2025</v>
       </c>
       <c r="C378" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D378" t="s">
         <v>8</v>
       </c>
       <c r="E378" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F378">
         <v>1375</v>
@@ -8243,13 +8243,13 @@
         <v>2025</v>
       </c>
       <c r="C379" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D379" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E379" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F379">
         <v>168</v>
@@ -8263,13 +8263,13 @@
         <v>2025</v>
       </c>
       <c r="C380" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D380" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E380" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F380">
         <v>394</v>
@@ -8303,13 +8303,13 @@
         <v>2026</v>
       </c>
       <c r="C382" t="s">
+        <v>76</v>
+      </c>
+      <c r="D382" t="s">
         <v>38</v>
       </c>
-      <c r="D382" t="s">
-        <v>39</v>
-      </c>
       <c r="E382" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F382">
         <v>1560</v>
@@ -8323,7 +8323,7 @@
         <v>2026</v>
       </c>
       <c r="C383" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D383" t="s">
         <v>8</v>
@@ -8349,7 +8349,7 @@
         <v>8</v>
       </c>
       <c r="E384" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F384">
         <v>1722</v>
@@ -8363,13 +8363,13 @@
         <v>2026</v>
       </c>
       <c r="C385" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D385" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E385" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F385">
         <v>45</v>
@@ -8403,13 +8403,13 @@
         <v>2026</v>
       </c>
       <c r="C387" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D387" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E387" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F387">
         <v>90</v>
@@ -8423,13 +8423,13 @@
         <v>2026</v>
       </c>
       <c r="C388" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D388" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E388" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F388">
         <v>95</v>
@@ -8443,13 +8443,13 @@
         <v>2026</v>
       </c>
       <c r="C389" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D389" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E389" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F389">
         <v>190</v>
@@ -8463,7 +8463,7 @@
         <v>2026</v>
       </c>
       <c r="C390" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D390" t="s">
         <v>8</v>
@@ -8503,13 +8503,13 @@
         <v>2026</v>
       </c>
       <c r="C392" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D392" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E392" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F392">
         <v>143</v>
@@ -8523,13 +8523,13 @@
         <v>2026</v>
       </c>
       <c r="C393" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D393" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E393" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F393">
         <v>559</v>
@@ -8549,7 +8549,7 @@
         <v>8</v>
       </c>
       <c r="E394" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F394">
         <v>1858</v>
@@ -8563,13 +8563,13 @@
         <v>2026</v>
       </c>
       <c r="C395" t="s">
+        <v>47</v>
+      </c>
+      <c r="D395" t="s">
+        <v>42</v>
+      </c>
+      <c r="E395" t="s">
         <v>48</v>
-      </c>
-      <c r="D395" t="s">
-        <v>43</v>
-      </c>
-      <c r="E395" t="s">
-        <v>49</v>
       </c>
       <c r="F395">
         <v>986</v>
@@ -8583,13 +8583,13 @@
         <v>2026</v>
       </c>
       <c r="C396" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D396" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E396" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F396">
         <v>592</v>
@@ -8623,13 +8623,13 @@
         <v>2026</v>
       </c>
       <c r="C398" t="s">
+        <v>51</v>
+      </c>
+      <c r="D398" t="s">
+        <v>42</v>
+      </c>
+      <c r="E398" t="s">
         <v>52</v>
-      </c>
-      <c r="D398" t="s">
-        <v>43</v>
-      </c>
-      <c r="E398" t="s">
-        <v>53</v>
       </c>
       <c r="F398">
         <v>355</v>
@@ -8649,7 +8649,7 @@
         <v>35</v>
       </c>
       <c r="E399" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F399">
         <v>2921</v>
@@ -8663,13 +8663,13 @@
         <v>2026</v>
       </c>
       <c r="C400" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D400" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E400" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F400">
         <v>3469</v>
@@ -8723,13 +8723,13 @@
         <v>2026</v>
       </c>
       <c r="C403" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D403" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E403" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F403">
         <v>121</v>
@@ -8749,7 +8749,7 @@
         <v>35</v>
       </c>
       <c r="E404" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F404">
         <v>4568</v>
@@ -8763,13 +8763,13 @@
         <v>2026</v>
       </c>
       <c r="C405" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D405" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E405" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F405">
         <v>1500</v>
@@ -8783,13 +8783,13 @@
         <v>2026</v>
       </c>
       <c r="C406" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D406" t="s">
         <v>8</v>
       </c>
       <c r="E406" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F406">
         <v>1375</v>
@@ -8803,13 +8803,13 @@
         <v>2026</v>
       </c>
       <c r="C407" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D407" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E407" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F407">
         <v>97</v>
@@ -8823,13 +8823,13 @@
         <v>2026</v>
       </c>
       <c r="C408" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D408" t="s">
         <v>8</v>
       </c>
       <c r="E408" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F408">
         <v>868</v>
@@ -8843,13 +8843,13 @@
         <v>2026</v>
       </c>
       <c r="C409" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D409" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E409" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F409">
         <v>140</v>
@@ -8863,13 +8863,13 @@
         <v>2026</v>
       </c>
       <c r="C410" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D410" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E410" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F410">
         <v>205</v>
@@ -8903,13 +8903,13 @@
         <v>2025</v>
       </c>
       <c r="C412" t="s">
+        <v>76</v>
+      </c>
+      <c r="D412" t="s">
         <v>38</v>
       </c>
-      <c r="D412" t="s">
-        <v>39</v>
-      </c>
       <c r="E412" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F412">
         <v>1820</v>
@@ -8929,7 +8929,7 @@
         <v>8</v>
       </c>
       <c r="E413" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F413">
         <v>1321</v>
@@ -8943,13 +8943,13 @@
         <v>2025</v>
       </c>
       <c r="C414" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D414" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E414" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F414">
         <v>436</v>
@@ -8963,13 +8963,13 @@
         <v>2025</v>
       </c>
       <c r="C415" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D415" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E415" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F415">
         <v>706</v>
@@ -9003,13 +9003,13 @@
         <v>2025</v>
       </c>
       <c r="C417" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D417" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E417" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F417">
         <v>712</v>
@@ -9023,13 +9023,13 @@
         <v>2025</v>
       </c>
       <c r="C418" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D418" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E418" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F418">
         <v>2510</v>
@@ -9049,7 +9049,7 @@
         <v>8</v>
       </c>
       <c r="E419" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F419">
         <v>1761</v>
@@ -9063,13 +9063,13 @@
         <v>2025</v>
       </c>
       <c r="C420" t="s">
+        <v>47</v>
+      </c>
+      <c r="D420" t="s">
+        <v>42</v>
+      </c>
+      <c r="E420" t="s">
         <v>48</v>
-      </c>
-      <c r="D420" t="s">
-        <v>43</v>
-      </c>
-      <c r="E420" t="s">
-        <v>49</v>
       </c>
       <c r="F420">
         <v>1416</v>
@@ -9083,13 +9083,13 @@
         <v>2025</v>
       </c>
       <c r="C421" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D421" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E421" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F421">
         <v>1935</v>
@@ -9123,13 +9123,13 @@
         <v>2025</v>
       </c>
       <c r="C423" t="s">
+        <v>51</v>
+      </c>
+      <c r="D423" t="s">
+        <v>42</v>
+      </c>
+      <c r="E423" t="s">
         <v>52</v>
-      </c>
-      <c r="D423" t="s">
-        <v>43</v>
-      </c>
-      <c r="E423" t="s">
-        <v>53</v>
       </c>
       <c r="F423">
         <v>396</v>
@@ -9149,7 +9149,7 @@
         <v>35</v>
       </c>
       <c r="E424" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F424">
         <v>2921</v>
@@ -9163,13 +9163,13 @@
         <v>2025</v>
       </c>
       <c r="C425" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D425" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E425" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F425">
         <v>3333</v>
@@ -9183,13 +9183,13 @@
         <v>2025</v>
       </c>
       <c r="C426" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D426" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E426" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F426">
         <v>400</v>
@@ -9203,13 +9203,13 @@
         <v>2025</v>
       </c>
       <c r="C427" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D427" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E427" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F427">
         <v>615</v>
@@ -9266,10 +9266,10 @@
         <v>30</v>
       </c>
       <c r="D430" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E430" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F430">
         <v>944</v>
@@ -9283,13 +9283,13 @@
         <v>2025</v>
       </c>
       <c r="C431" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D431" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E431" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F431">
         <v>2419</v>
@@ -9309,7 +9309,7 @@
         <v>35</v>
       </c>
       <c r="E432" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F432">
         <v>4073</v>
@@ -9323,13 +9323,13 @@
         <v>2025</v>
       </c>
       <c r="C433" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D433" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E433" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F433">
         <v>1645</v>
@@ -9363,13 +9363,13 @@
         <v>2025</v>
       </c>
       <c r="C435" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D435" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E435" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F435">
         <v>366</v>
@@ -9383,13 +9383,13 @@
         <v>2025</v>
       </c>
       <c r="C436" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D436" t="s">
         <v>8</v>
       </c>
       <c r="E436" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F436">
         <v>1375</v>
@@ -9423,13 +9423,13 @@
         <v>2025</v>
       </c>
       <c r="C438" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D438" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E438" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F438">
         <v>2002</v>
@@ -9443,13 +9443,13 @@
         <v>2025</v>
       </c>
       <c r="C439" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D439" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E439" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F439">
         <v>1063</v>
@@ -9463,13 +9463,13 @@
         <v>2025</v>
       </c>
       <c r="C440" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D440" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E440" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F440">
         <v>300</v>
@@ -9483,13 +9483,13 @@
         <v>2025</v>
       </c>
       <c r="C441" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D441" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E441" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F441">
         <v>519</v>
@@ -9523,13 +9523,13 @@
         <v>2026</v>
       </c>
       <c r="C443" t="s">
+        <v>76</v>
+      </c>
+      <c r="D443" t="s">
         <v>38</v>
       </c>
-      <c r="D443" t="s">
-        <v>39</v>
-      </c>
       <c r="E443" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F443">
         <v>1560</v>
@@ -9543,7 +9543,7 @@
         <v>2026</v>
       </c>
       <c r="C444" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D444" t="s">
         <v>8</v>
@@ -9569,7 +9569,7 @@
         <v>8</v>
       </c>
       <c r="E445" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F445">
         <v>1707</v>
@@ -9583,13 +9583,13 @@
         <v>2026</v>
       </c>
       <c r="C446" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D446" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E446" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F446">
         <v>485</v>
@@ -9623,13 +9623,13 @@
         <v>2026</v>
       </c>
       <c r="C448" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D448" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E448" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F448">
         <v>395</v>
@@ -9643,13 +9643,13 @@
         <v>2026</v>
       </c>
       <c r="C449" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D449" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E449" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F449">
         <v>223</v>
@@ -9663,13 +9663,13 @@
         <v>2026</v>
       </c>
       <c r="C450" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D450" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E450" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F450">
         <v>0</v>
@@ -9703,13 +9703,13 @@
         <v>2026</v>
       </c>
       <c r="C452" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D452" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E452" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F452">
         <v>209</v>
@@ -9723,13 +9723,13 @@
         <v>2026</v>
       </c>
       <c r="C453" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D453" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E453" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F453">
         <v>1511</v>
@@ -9749,7 +9749,7 @@
         <v>8</v>
       </c>
       <c r="E454" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F454">
         <v>1203</v>
@@ -9763,13 +9763,13 @@
         <v>2026</v>
       </c>
       <c r="C455" t="s">
+        <v>47</v>
+      </c>
+      <c r="D455" t="s">
+        <v>42</v>
+      </c>
+      <c r="E455" t="s">
         <v>48</v>
-      </c>
-      <c r="D455" t="s">
-        <v>43</v>
-      </c>
-      <c r="E455" t="s">
-        <v>49</v>
       </c>
       <c r="F455">
         <v>1860</v>
@@ -9783,13 +9783,13 @@
         <v>2026</v>
       </c>
       <c r="C456" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D456" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E456" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F456">
         <v>1158</v>
@@ -9803,13 +9803,13 @@
         <v>2026</v>
       </c>
       <c r="C457" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D457" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E457" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F457">
         <v>1489</v>
@@ -9843,13 +9843,13 @@
         <v>2026</v>
       </c>
       <c r="C459" t="s">
+        <v>51</v>
+      </c>
+      <c r="D459" t="s">
+        <v>42</v>
+      </c>
+      <c r="E459" t="s">
         <v>52</v>
-      </c>
-      <c r="D459" t="s">
-        <v>43</v>
-      </c>
-      <c r="E459" t="s">
-        <v>53</v>
       </c>
       <c r="F459">
         <v>324</v>
@@ -9869,7 +9869,7 @@
         <v>35</v>
       </c>
       <c r="E460" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F460">
         <v>3324</v>
@@ -9883,13 +9883,13 @@
         <v>2026</v>
       </c>
       <c r="C461" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D461" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E461" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F461">
         <v>3571</v>
@@ -9903,13 +9903,13 @@
         <v>2026</v>
       </c>
       <c r="C462" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D462" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E462" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F462">
         <v>508</v>
@@ -9966,10 +9966,10 @@
         <v>30</v>
       </c>
       <c r="D465" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E465" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F465">
         <v>1612</v>
@@ -9983,13 +9983,13 @@
         <v>2026</v>
       </c>
       <c r="C466" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D466" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E466" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F466">
         <v>1678</v>
@@ -10009,7 +10009,7 @@
         <v>35</v>
       </c>
       <c r="E467" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F467">
         <v>4353</v>
@@ -10023,13 +10023,13 @@
         <v>2026</v>
       </c>
       <c r="C468" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D468" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E468" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F468">
         <v>1645</v>
@@ -10043,13 +10043,13 @@
         <v>2026</v>
       </c>
       <c r="C469" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D469" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E469" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F469">
         <v>3291</v>
@@ -10103,13 +10103,13 @@
         <v>2026</v>
       </c>
       <c r="C472" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D472" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E472" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F472">
         <v>195</v>
@@ -10123,13 +10123,13 @@
         <v>2026</v>
       </c>
       <c r="C473" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D473" t="s">
         <v>8</v>
       </c>
       <c r="E473" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F473">
         <v>1375</v>
@@ -10143,13 +10143,13 @@
         <v>2026</v>
       </c>
       <c r="C474" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D474" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E474" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F474">
         <v>275</v>
@@ -10163,13 +10163,13 @@
         <v>2026</v>
       </c>
       <c r="C475" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D475" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E475" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F475">
         <v>1611</v>
@@ -10183,13 +10183,13 @@
         <v>2026</v>
       </c>
       <c r="C476" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D476" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E476" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F476">
         <v>868</v>
@@ -10203,13 +10203,13 @@
         <v>2026</v>
       </c>
       <c r="C477" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D477" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E477" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F477">
         <v>1118</v>
@@ -10223,13 +10223,13 @@
         <v>2026</v>
       </c>
       <c r="C478" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D478" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E478" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F478">
         <v>165</v>
@@ -10243,13 +10243,13 @@
         <v>2026</v>
       </c>
       <c r="C479" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D479" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E479" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F479">
         <v>360</v>
@@ -10263,13 +10263,13 @@
         <v>2026</v>
       </c>
       <c r="C480" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D480" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E480" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F480">
         <v>340</v>
@@ -10303,13 +10303,13 @@
         <v>2025</v>
       </c>
       <c r="C482" t="s">
+        <v>76</v>
+      </c>
+      <c r="D482" t="s">
         <v>38</v>
       </c>
-      <c r="D482" t="s">
-        <v>39</v>
-      </c>
       <c r="E482" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F482">
         <v>1820</v>
@@ -10329,7 +10329,7 @@
         <v>8</v>
       </c>
       <c r="E483" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F483">
         <v>1426</v>
@@ -10343,13 +10343,13 @@
         <v>2025</v>
       </c>
       <c r="C484" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D484" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E484" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F484">
         <v>154</v>
@@ -10363,13 +10363,13 @@
         <v>2025</v>
       </c>
       <c r="C485" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D485" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E485" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F485">
         <v>604</v>
@@ -10403,13 +10403,13 @@
         <v>2025</v>
       </c>
       <c r="C487" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D487" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E487" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F487">
         <v>591</v>
@@ -10423,13 +10423,13 @@
         <v>2025</v>
       </c>
       <c r="C488" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D488" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E488" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F488">
         <v>2286</v>
@@ -10449,7 +10449,7 @@
         <v>8</v>
       </c>
       <c r="E489" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F489">
         <v>1499</v>
@@ -10463,13 +10463,13 @@
         <v>2025</v>
       </c>
       <c r="C490" t="s">
+        <v>47</v>
+      </c>
+      <c r="D490" t="s">
+        <v>42</v>
+      </c>
+      <c r="E490" t="s">
         <v>48</v>
-      </c>
-      <c r="D490" t="s">
-        <v>43</v>
-      </c>
-      <c r="E490" t="s">
-        <v>49</v>
       </c>
       <c r="F490">
         <v>1932</v>
@@ -10483,13 +10483,13 @@
         <v>2025</v>
       </c>
       <c r="C491" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D491" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E491" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F491">
         <v>2050</v>
@@ -10523,13 +10523,13 @@
         <v>2025</v>
       </c>
       <c r="C493" t="s">
+        <v>51</v>
+      </c>
+      <c r="D493" t="s">
+        <v>42</v>
+      </c>
+      <c r="E493" t="s">
         <v>52</v>
-      </c>
-      <c r="D493" t="s">
-        <v>43</v>
-      </c>
-      <c r="E493" t="s">
-        <v>53</v>
       </c>
       <c r="F493">
         <v>768</v>
@@ -10549,7 +10549,7 @@
         <v>35</v>
       </c>
       <c r="E494" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F494">
         <v>2918</v>
@@ -10563,13 +10563,13 @@
         <v>2025</v>
       </c>
       <c r="C495" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D495" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E495" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F495">
         <v>3333</v>
@@ -10583,13 +10583,13 @@
         <v>2025</v>
       </c>
       <c r="C496" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D496" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E496" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F496">
         <v>489</v>
@@ -10603,13 +10603,13 @@
         <v>2025</v>
       </c>
       <c r="C497" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D497" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E497" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F497">
         <v>619</v>
@@ -10666,10 +10666,10 @@
         <v>30</v>
       </c>
       <c r="D500" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E500" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F500">
         <v>730</v>
@@ -10683,13 +10683,13 @@
         <v>2025</v>
       </c>
       <c r="C501" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D501" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E501" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F501">
         <v>4388</v>
@@ -10709,7 +10709,7 @@
         <v>35</v>
       </c>
       <c r="E502" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F502">
         <v>4078</v>
@@ -10723,13 +10723,13 @@
         <v>2025</v>
       </c>
       <c r="C503" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D503" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E503" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F503">
         <v>1500</v>
@@ -10763,13 +10763,13 @@
         <v>2025</v>
       </c>
       <c r="C505" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D505" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E505" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F505">
         <v>455</v>
@@ -10783,13 +10783,13 @@
         <v>2025</v>
       </c>
       <c r="C506" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D506" t="s">
         <v>8</v>
       </c>
       <c r="E506" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F506">
         <v>1254</v>
@@ -10823,13 +10823,13 @@
         <v>2025</v>
       </c>
       <c r="C508" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D508" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E508" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F508">
         <v>999</v>
@@ -10843,13 +10843,13 @@
         <v>2025</v>
       </c>
       <c r="C509" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D509" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E509" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F509">
         <v>1114</v>
@@ -10863,13 +10863,13 @@
         <v>2025</v>
       </c>
       <c r="C510" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D510" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E510" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F510">
         <v>380</v>
@@ -10883,13 +10883,13 @@
         <v>2025</v>
       </c>
       <c r="C511" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D511" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E511" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F511">
         <v>271</v>
@@ -10923,13 +10923,13 @@
         <v>2026</v>
       </c>
       <c r="C513" t="s">
+        <v>76</v>
+      </c>
+      <c r="D513" t="s">
         <v>38</v>
       </c>
-      <c r="D513" t="s">
-        <v>39</v>
-      </c>
       <c r="E513" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F513">
         <v>1560</v>
@@ -10949,7 +10949,7 @@
         <v>8</v>
       </c>
       <c r="E514" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F514">
         <v>1632</v>
@@ -10963,13 +10963,13 @@
         <v>2026</v>
       </c>
       <c r="C515" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D515" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E515" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F515">
         <v>553</v>
@@ -11003,13 +11003,13 @@
         <v>2026</v>
       </c>
       <c r="C517" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D517" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E517" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F517">
         <v>448</v>
@@ -11023,13 +11023,13 @@
         <v>2026</v>
       </c>
       <c r="C518" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D518" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E518" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F518">
         <v>385</v>
@@ -11043,13 +11043,13 @@
         <v>2026</v>
       </c>
       <c r="C519" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D519" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E519" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F519">
         <v>100</v>
@@ -11083,13 +11083,13 @@
         <v>2026</v>
       </c>
       <c r="C521" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D521" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E521" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F521">
         <v>610</v>
@@ -11103,13 +11103,13 @@
         <v>2026</v>
       </c>
       <c r="C522" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D522" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E522" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F522">
         <v>2069</v>
@@ -11129,7 +11129,7 @@
         <v>8</v>
       </c>
       <c r="E523" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F523">
         <v>814</v>
@@ -11143,13 +11143,13 @@
         <v>2026</v>
       </c>
       <c r="C524" t="s">
+        <v>47</v>
+      </c>
+      <c r="D524" t="s">
+        <v>42</v>
+      </c>
+      <c r="E524" t="s">
         <v>48</v>
-      </c>
-      <c r="D524" t="s">
-        <v>43</v>
-      </c>
-      <c r="E524" t="s">
-        <v>49</v>
       </c>
       <c r="F524">
         <v>2489</v>
@@ -11163,13 +11163,13 @@
         <v>2026</v>
       </c>
       <c r="C525" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D525" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E525" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F525">
         <v>1460</v>
@@ -11183,13 +11183,13 @@
         <v>2026</v>
       </c>
       <c r="C526" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D526" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E526" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F526">
         <v>1643</v>
@@ -11223,13 +11223,13 @@
         <v>2026</v>
       </c>
       <c r="C528" t="s">
+        <v>51</v>
+      </c>
+      <c r="D528" t="s">
+        <v>42</v>
+      </c>
+      <c r="E528" t="s">
         <v>52</v>
-      </c>
-      <c r="D528" t="s">
-        <v>43</v>
-      </c>
-      <c r="E528" t="s">
-        <v>53</v>
       </c>
       <c r="F528">
         <v>762</v>
@@ -11249,7 +11249,7 @@
         <v>35</v>
       </c>
       <c r="E529" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F529">
         <v>3844</v>
@@ -11263,13 +11263,13 @@
         <v>2026</v>
       </c>
       <c r="C530" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D530" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E530" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F530">
         <v>3550</v>
@@ -11283,13 +11283,13 @@
         <v>2026</v>
       </c>
       <c r="C531" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D531" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E531" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F531">
         <v>553</v>
@@ -11346,10 +11346,10 @@
         <v>30</v>
       </c>
       <c r="D534" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E534" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F534">
         <v>2601</v>
@@ -11363,13 +11363,13 @@
         <v>2026</v>
       </c>
       <c r="C535" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D535" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E535" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F535">
         <v>2243</v>
@@ -11389,7 +11389,7 @@
         <v>35</v>
       </c>
       <c r="E536" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F536">
         <v>4338</v>
@@ -11403,13 +11403,13 @@
         <v>2026</v>
       </c>
       <c r="C537" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D537" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E537" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F537">
         <v>1500</v>
@@ -11463,13 +11463,13 @@
         <v>2026</v>
       </c>
       <c r="C540" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D540" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E540" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F540">
         <v>285</v>
@@ -11483,13 +11483,13 @@
         <v>2026</v>
       </c>
       <c r="C541" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D541" t="s">
         <v>8</v>
       </c>
       <c r="E541" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F541">
         <v>1254</v>
@@ -11503,13 +11503,13 @@
         <v>2026</v>
       </c>
       <c r="C542" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D542" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E542" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F542">
         <v>218</v>
@@ -11523,13 +11523,13 @@
         <v>2026</v>
       </c>
       <c r="C543" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D543" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E543" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F543">
         <v>575</v>
@@ -11543,13 +11543,13 @@
         <v>2026</v>
       </c>
       <c r="C544" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D544" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E544" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F544">
         <v>1386</v>
@@ -11563,13 +11563,13 @@
         <v>2026</v>
       </c>
       <c r="C545" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D545" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E545" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F545">
         <v>818</v>
@@ -11583,13 +11583,13 @@
         <v>2026</v>
       </c>
       <c r="C546" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D546" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E546" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F546">
         <v>305</v>
@@ -11603,13 +11603,13 @@
         <v>2026</v>
       </c>
       <c r="C547" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D547" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E547" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F547">
         <v>528</v>
@@ -11643,13 +11643,13 @@
         <v>2025</v>
       </c>
       <c r="C549" t="s">
+        <v>76</v>
+      </c>
+      <c r="D549" t="s">
         <v>38</v>
       </c>
-      <c r="D549" t="s">
-        <v>39</v>
-      </c>
       <c r="E549" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F549">
         <v>1560</v>
@@ -11669,7 +11669,7 @@
         <v>8</v>
       </c>
       <c r="E550" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F550">
         <v>1362</v>
@@ -11703,13 +11703,13 @@
         <v>2025</v>
       </c>
       <c r="C552" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D552" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E552" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F552">
         <v>318</v>
@@ -11723,13 +11723,13 @@
         <v>2025</v>
       </c>
       <c r="C553" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D553" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E553" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F553">
         <v>205</v>
@@ -11763,13 +11763,13 @@
         <v>2025</v>
       </c>
       <c r="C555" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D555" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E555" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F555">
         <v>188</v>
@@ -11803,13 +11803,13 @@
         <v>2025</v>
       </c>
       <c r="C557" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D557" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E557" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F557">
         <v>1910</v>
@@ -11829,7 +11829,7 @@
         <v>8</v>
       </c>
       <c r="E558" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F558">
         <v>1299</v>
@@ -11843,13 +11843,13 @@
         <v>2025</v>
       </c>
       <c r="C559" t="s">
+        <v>47</v>
+      </c>
+      <c r="D559" t="s">
+        <v>42</v>
+      </c>
+      <c r="E559" t="s">
         <v>48</v>
-      </c>
-      <c r="D559" t="s">
-        <v>43</v>
-      </c>
-      <c r="E559" t="s">
-        <v>49</v>
       </c>
       <c r="F559">
         <v>1872</v>
@@ -11863,13 +11863,13 @@
         <v>2025</v>
       </c>
       <c r="C560" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D560" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E560" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F560">
         <v>1009</v>
@@ -11883,13 +11883,13 @@
         <v>2025</v>
       </c>
       <c r="C561" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D561" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E561" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F561">
         <v>1763</v>
@@ -11923,13 +11923,13 @@
         <v>2025</v>
       </c>
       <c r="C563" t="s">
+        <v>51</v>
+      </c>
+      <c r="D563" t="s">
+        <v>42</v>
+      </c>
+      <c r="E563" t="s">
         <v>52</v>
-      </c>
-      <c r="D563" t="s">
-        <v>43</v>
-      </c>
-      <c r="E563" t="s">
-        <v>53</v>
       </c>
       <c r="F563">
         <v>704</v>
@@ -11949,7 +11949,7 @@
         <v>35</v>
       </c>
       <c r="E564" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F564">
         <v>3488</v>
@@ -11963,13 +11963,13 @@
         <v>2025</v>
       </c>
       <c r="C565" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D565" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E565" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F565">
         <v>3333</v>
@@ -11983,13 +11983,13 @@
         <v>2025</v>
       </c>
       <c r="C566" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D566" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E566" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F566">
         <v>541</v>
@@ -12063,13 +12063,13 @@
         <v>2025</v>
       </c>
       <c r="C570" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D570" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E570" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F570">
         <v>2002</v>
@@ -12089,7 +12089,7 @@
         <v>35</v>
       </c>
       <c r="E571" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F571">
         <v>3761</v>
@@ -12103,13 +12103,13 @@
         <v>2025</v>
       </c>
       <c r="C572" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D572" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E572" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F572">
         <v>1645</v>
@@ -12163,13 +12163,13 @@
         <v>2025</v>
       </c>
       <c r="C575" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D575" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E575" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F575">
         <v>256</v>
@@ -12183,13 +12183,13 @@
         <v>2025</v>
       </c>
       <c r="C576" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D576" t="s">
         <v>8</v>
       </c>
       <c r="E576" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F576">
         <v>1375</v>
@@ -12203,13 +12203,13 @@
         <v>2025</v>
       </c>
       <c r="C577" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D577" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E577" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F577">
         <v>324</v>
@@ -12223,13 +12223,13 @@
         <v>2025</v>
       </c>
       <c r="C578" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D578" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E578" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F578">
         <v>1687</v>
@@ -12243,13 +12243,13 @@
         <v>2025</v>
       </c>
       <c r="C579" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D579" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E579" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F579">
         <v>815</v>
@@ -12263,13 +12263,13 @@
         <v>2025</v>
       </c>
       <c r="C580" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D580" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E580" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F580">
         <v>622</v>
@@ -12283,13 +12283,13 @@
         <v>2025</v>
       </c>
       <c r="C581" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D581" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E581" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F581">
         <v>122</v>
@@ -12303,13 +12303,13 @@
         <v>2025</v>
       </c>
       <c r="C582" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D582" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E582" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F582">
         <v>171</v>
@@ -12343,13 +12343,13 @@
         <v>2025</v>
       </c>
       <c r="C584" t="s">
+        <v>76</v>
+      </c>
+      <c r="D584" t="s">
         <v>38</v>
       </c>
-      <c r="D584" t="s">
-        <v>39</v>
-      </c>
       <c r="E584" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F584">
         <v>1560</v>
@@ -12369,7 +12369,7 @@
         <v>8</v>
       </c>
       <c r="E585" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F585">
         <v>1321</v>
@@ -12403,13 +12403,13 @@
         <v>2025</v>
       </c>
       <c r="C587" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D587" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E587" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F587">
         <v>180</v>
@@ -12423,13 +12423,13 @@
         <v>2025</v>
       </c>
       <c r="C588" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D588" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E588" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F588">
         <v>150</v>
@@ -12443,13 +12443,13 @@
         <v>2025</v>
       </c>
       <c r="C589" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D589" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E589" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F589">
         <v>88</v>
@@ -12483,13 +12483,13 @@
         <v>2025</v>
       </c>
       <c r="C591" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D591" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E591" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F591">
         <v>608</v>
@@ -12523,13 +12523,13 @@
         <v>2025</v>
       </c>
       <c r="C593" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D593" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E593" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F593">
         <v>1667</v>
@@ -12549,7 +12549,7 @@
         <v>8</v>
       </c>
       <c r="E594" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F594">
         <v>1370</v>
@@ -12563,13 +12563,13 @@
         <v>2025</v>
       </c>
       <c r="C595" t="s">
+        <v>47</v>
+      </c>
+      <c r="D595" t="s">
+        <v>42</v>
+      </c>
+      <c r="E595" t="s">
         <v>48</v>
-      </c>
-      <c r="D595" t="s">
-        <v>43</v>
-      </c>
-      <c r="E595" t="s">
-        <v>49</v>
       </c>
       <c r="F595">
         <v>2942</v>
@@ -12583,13 +12583,13 @@
         <v>2025</v>
       </c>
       <c r="C596" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D596" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E596" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F596">
         <v>617</v>
@@ -12603,13 +12603,13 @@
         <v>2025</v>
       </c>
       <c r="C597" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D597" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E597" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F597">
         <v>1835</v>
@@ -12643,13 +12643,13 @@
         <v>2025</v>
       </c>
       <c r="C599" t="s">
+        <v>51</v>
+      </c>
+      <c r="D599" t="s">
+        <v>42</v>
+      </c>
+      <c r="E599" t="s">
         <v>52</v>
-      </c>
-      <c r="D599" t="s">
-        <v>43</v>
-      </c>
-      <c r="E599" t="s">
-        <v>53</v>
       </c>
       <c r="F599">
         <v>1100</v>
@@ -12669,7 +12669,7 @@
         <v>35</v>
       </c>
       <c r="E600" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F600">
         <v>2910</v>
@@ -12683,13 +12683,13 @@
         <v>2025</v>
       </c>
       <c r="C601" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D601" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E601" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F601">
         <v>3333</v>
@@ -12703,13 +12703,13 @@
         <v>2025</v>
       </c>
       <c r="C602" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D602" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E602" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F602">
         <v>681</v>
@@ -12783,13 +12783,13 @@
         <v>2025</v>
       </c>
       <c r="C606" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D606" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E606" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F606">
         <v>2002</v>
@@ -12809,7 +12809,7 @@
         <v>35</v>
       </c>
       <c r="E607" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F607">
         <v>4547</v>
@@ -12823,13 +12823,13 @@
         <v>2025</v>
       </c>
       <c r="C608" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D608" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E608" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F608">
         <v>2194</v>
@@ -12883,13 +12883,13 @@
         <v>2025</v>
       </c>
       <c r="C611" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D611" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E611" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F611">
         <v>387</v>
@@ -12903,13 +12903,13 @@
         <v>2025</v>
       </c>
       <c r="C612" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D612" t="s">
         <v>8</v>
       </c>
       <c r="E612" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F612">
         <v>1376</v>
@@ -12923,13 +12923,13 @@
         <v>2025</v>
       </c>
       <c r="C613" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D613" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E613" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F613">
         <v>240</v>
@@ -12943,13 +12943,13 @@
         <v>2025</v>
       </c>
       <c r="C614" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D614" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E614" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F614">
         <v>2039</v>
@@ -12963,13 +12963,13 @@
         <v>2025</v>
       </c>
       <c r="C615" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D615" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E615" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F615">
         <v>997</v>
@@ -12983,13 +12983,13 @@
         <v>2025</v>
       </c>
       <c r="C616" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D616" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E616" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F616">
         <v>679</v>
@@ -13003,13 +13003,13 @@
         <v>2025</v>
       </c>
       <c r="C617" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D617" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E617" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F617">
         <v>354</v>
@@ -13023,13 +13023,13 @@
         <v>2025</v>
       </c>
       <c r="C618" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D618" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E618" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F618">
         <v>183</v>
@@ -13063,13 +13063,13 @@
         <v>2025</v>
       </c>
       <c r="C620" t="s">
+        <v>76</v>
+      </c>
+      <c r="D620" t="s">
         <v>38</v>
       </c>
-      <c r="D620" t="s">
-        <v>39</v>
-      </c>
       <c r="E620" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F620">
         <v>1560</v>
@@ -13089,7 +13089,7 @@
         <v>8</v>
       </c>
       <c r="E621" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F621">
         <v>2382</v>
@@ -13123,13 +13123,13 @@
         <v>2025</v>
       </c>
       <c r="C623" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D623" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E623" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F623">
         <v>543</v>
@@ -13163,13 +13163,13 @@
         <v>2025</v>
       </c>
       <c r="C625" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D625" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E625" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F625">
         <v>778</v>
@@ -13203,13 +13203,13 @@
         <v>2025</v>
       </c>
       <c r="C627" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D627" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E627" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F627">
         <v>1822</v>
@@ -13229,7 +13229,7 @@
         <v>8</v>
       </c>
       <c r="E628" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F628">
         <v>416</v>
@@ -13243,13 +13243,13 @@
         <v>2025</v>
       </c>
       <c r="C629" t="s">
+        <v>47</v>
+      </c>
+      <c r="D629" t="s">
+        <v>42</v>
+      </c>
+      <c r="E629" t="s">
         <v>48</v>
-      </c>
-      <c r="D629" t="s">
-        <v>43</v>
-      </c>
-      <c r="E629" t="s">
-        <v>49</v>
       </c>
       <c r="F629">
         <v>1828</v>
@@ -13263,13 +13263,13 @@
         <v>2025</v>
       </c>
       <c r="C630" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D630" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E630" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F630">
         <v>1056</v>
@@ -13283,13 +13283,13 @@
         <v>2025</v>
       </c>
       <c r="C631" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D631" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E631" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F631">
         <v>1232</v>
@@ -13323,13 +13323,13 @@
         <v>2025</v>
       </c>
       <c r="C633" t="s">
+        <v>51</v>
+      </c>
+      <c r="D633" t="s">
+        <v>42</v>
+      </c>
+      <c r="E633" t="s">
         <v>52</v>
-      </c>
-      <c r="D633" t="s">
-        <v>43</v>
-      </c>
-      <c r="E633" t="s">
-        <v>53</v>
       </c>
       <c r="F633">
         <v>552</v>
@@ -13349,7 +13349,7 @@
         <v>35</v>
       </c>
       <c r="E634" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F634">
         <v>3849</v>
@@ -13363,13 +13363,13 @@
         <v>2025</v>
       </c>
       <c r="C635" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D635" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E635" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F635">
         <v>3833</v>
@@ -13383,13 +13383,13 @@
         <v>2025</v>
       </c>
       <c r="C636" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D636" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E636" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F636">
         <v>460</v>
@@ -13466,10 +13466,10 @@
         <v>30</v>
       </c>
       <c r="D640" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E640" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F640">
         <v>1746</v>
@@ -13483,13 +13483,13 @@
         <v>2025</v>
       </c>
       <c r="C641" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D641" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E641" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F641">
         <v>116</v>
@@ -13509,7 +13509,7 @@
         <v>35</v>
       </c>
       <c r="E642" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F642">
         <v>4816</v>
@@ -13523,13 +13523,13 @@
         <v>2025</v>
       </c>
       <c r="C643" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D643" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E643" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F643">
         <v>1645</v>
@@ -13583,13 +13583,13 @@
         <v>2025</v>
       </c>
       <c r="C646" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D646" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E646" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F646">
         <v>69</v>
@@ -13603,13 +13603,13 @@
         <v>2025</v>
       </c>
       <c r="C647" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D647" t="s">
         <v>8</v>
       </c>
       <c r="E647" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F647">
         <v>1375</v>
@@ -13623,13 +13623,13 @@
         <v>2025</v>
       </c>
       <c r="C648" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D648" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E648" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F648">
         <v>389</v>
@@ -13643,13 +13643,13 @@
         <v>2025</v>
       </c>
       <c r="C649" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D649" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E649" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F649">
         <v>1838</v>
@@ -13663,13 +13663,13 @@
         <v>2025</v>
       </c>
       <c r="C650" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D650" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E650" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F650">
         <v>435</v>
@@ -13683,13 +13683,13 @@
         <v>2025</v>
       </c>
       <c r="C651" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D651" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E651" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F651">
         <v>1521</v>
@@ -13703,13 +13703,13 @@
         <v>2025</v>
       </c>
       <c r="C652" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D652" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E652" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F652">
         <v>323</v>
@@ -13743,13 +13743,13 @@
         <v>2026</v>
       </c>
       <c r="C654" t="s">
+        <v>76</v>
+      </c>
+      <c r="D654" t="s">
         <v>38</v>
       </c>
-      <c r="D654" t="s">
-        <v>39</v>
-      </c>
       <c r="E654" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F654">
         <v>1560</v>
@@ -13763,7 +13763,7 @@
         <v>2026</v>
       </c>
       <c r="C655" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D655" t="s">
         <v>8</v>
@@ -13789,7 +13789,7 @@
         <v>8</v>
       </c>
       <c r="E656" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F656">
         <v>3357.05</v>
@@ -13803,13 +13803,13 @@
         <v>2026</v>
       </c>
       <c r="C657" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D657" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E657" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F657">
         <v>542.5</v>
@@ -13843,13 +13843,13 @@
         <v>2026</v>
       </c>
       <c r="C659" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D659" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E659" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F659">
         <v>565</v>
@@ -13863,13 +13863,13 @@
         <v>2026</v>
       </c>
       <c r="C660" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D660" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E660" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F660">
         <v>887.5</v>
@@ -13883,13 +13883,13 @@
         <v>2026</v>
       </c>
       <c r="C661" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D661" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E661" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F661">
         <v>605</v>
@@ -13903,7 +13903,7 @@
         <v>2026</v>
       </c>
       <c r="C662" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D662" t="s">
         <v>8</v>
@@ -13943,13 +13943,13 @@
         <v>2026</v>
       </c>
       <c r="C664" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D664" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E664" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F664">
         <v>1801.06</v>
@@ -13969,7 +13969,7 @@
         <v>8</v>
       </c>
       <c r="E665" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F665">
         <v>2000.26</v>
@@ -13983,13 +13983,13 @@
         <v>2026</v>
       </c>
       <c r="C666" t="s">
+        <v>47</v>
+      </c>
+      <c r="D666" t="s">
+        <v>42</v>
+      </c>
+      <c r="E666" t="s">
         <v>48</v>
-      </c>
-      <c r="D666" t="s">
-        <v>43</v>
-      </c>
-      <c r="E666" t="s">
-        <v>49</v>
       </c>
       <c r="F666">
         <v>3863.99</v>
@@ -14003,13 +14003,13 @@
         <v>2026</v>
       </c>
       <c r="C667" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D667" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E667" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F667">
         <v>1168.1600000000001</v>
@@ -14043,13 +14043,13 @@
         <v>2026</v>
       </c>
       <c r="C669" t="s">
+        <v>51</v>
+      </c>
+      <c r="D669" t="s">
+        <v>42</v>
+      </c>
+      <c r="E669" t="s">
         <v>52</v>
-      </c>
-      <c r="D669" t="s">
-        <v>43</v>
-      </c>
-      <c r="E669" t="s">
-        <v>53</v>
       </c>
       <c r="F669">
         <v>1625.56</v>
@@ -14069,7 +14069,7 @@
         <v>35</v>
       </c>
       <c r="E670" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F670">
         <v>4570.33</v>
@@ -14083,13 +14083,13 @@
         <v>2026</v>
       </c>
       <c r="C671" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D671" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E671" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F671">
         <v>3877.66</v>
@@ -14143,13 +14143,13 @@
         <v>2026</v>
       </c>
       <c r="C674" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D674" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E674" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F674">
         <v>2490.27</v>
@@ -14169,7 +14169,7 @@
         <v>35</v>
       </c>
       <c r="E675" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F675">
         <v>4675.33</v>
@@ -14183,13 +14183,13 @@
         <v>2026</v>
       </c>
       <c r="C676" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D676" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E676" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F676">
         <v>1809.81</v>
@@ -14203,13 +14203,13 @@
         <v>2026</v>
       </c>
       <c r="C677" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D677" t="s">
         <v>8</v>
       </c>
       <c r="E677" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F677">
         <v>1375.06</v>
@@ -14223,13 +14223,13 @@
         <v>2026</v>
       </c>
       <c r="C678" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D678" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E678" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F678">
         <v>1805.76</v>
@@ -14243,13 +14243,13 @@
         <v>2026</v>
       </c>
       <c r="C679" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D679" t="s">
         <v>8</v>
       </c>
       <c r="E679" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F679">
         <v>903.99</v>
@@ -14263,13 +14263,13 @@
         <v>2026</v>
       </c>
       <c r="C680" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D680" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E680" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F680">
         <v>1540</v>
@@ -14283,13 +14283,13 @@
         <v>2026</v>
       </c>
       <c r="C681" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D681" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E681" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F681">
         <v>582.5</v>
@@ -14303,13 +14303,13 @@
         <v>2026</v>
       </c>
       <c r="C682" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D682" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E682" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F682">
         <v>1082.5</v>
@@ -14323,13 +14323,13 @@
         <v>2026</v>
       </c>
       <c r="C683" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D683" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E683" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F683">
         <v>15</v>
@@ -14343,13 +14343,13 @@
         <v>2026</v>
       </c>
       <c r="C684" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D684" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E684" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F684">
         <v>490</v>
@@ -14363,13 +14363,13 @@
         <v>2026</v>
       </c>
       <c r="C685" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D685" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E685" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F685">
         <v>1294.3</v>
@@ -14383,13 +14383,13 @@
         <v>2026</v>
       </c>
       <c r="C686" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D686" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E686" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F686">
         <v>565</v>
